--- a/Gestion Stock 2026/BRH 2026/Fiche de Stock Global 2026.xlsx
+++ b/Gestion Stock 2026/BRH 2026/Fiche de Stock Global 2026.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\BRH 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCB863D-AFE3-4541-96B5-B2C6B6FE0F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DC0FB8-5554-4A70-A6B7-7E2E2A55E17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="13" r:id="rId1"/>
+    <sheet name="FEVRIER 2026" sheetId="14" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="31">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -165,6 +166,30 @@
   <si>
     <t>10 Compteurs DN 15/21 Destination Centre Beni Slimane</t>
   </si>
+  <si>
+    <r>
+      <t>Mois de FEVRIER</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -898,7 +923,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1084,6 +1109,68 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1117,67 +1204,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1221,6 +1250,139 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5581650" y="7705725"/>
+          <a:ext cx="958850" cy="1257300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>473075</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF7AA404-A82D-450F-96D9-5810DB508A3B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1629,58 +1791,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
-      <c r="G1" s="55" t="s">
+      <c r="G1" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
       <c r="E2" s="22"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="56" t="s">
+      <c r="G2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
       <c r="E3" s="22"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
     </row>
     <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -1697,61 +1859,61 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62" t="s">
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="63" t="s">
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="83" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58"/>
+      <c r="A8" s="78"/>
       <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
@@ -1782,7 +1944,7 @@
       <c r="K8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="64"/>
+      <c r="L8" s="84"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
@@ -2657,149 +2819,149 @@
       <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="66" t="s">
+      <c r="A42" s="67"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67" t="s">
+      <c r="H42" s="69"/>
+      <c r="I42" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="68"/>
+      <c r="J42" s="70"/>
       <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="71">
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="65">
         <v>447</v>
       </c>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="74"/>
+      <c r="H43" s="71"/>
+      <c r="I43" s="72"/>
+      <c r="J43" s="73"/>
       <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="75">
-        <v>0</v>
-      </c>
-      <c r="H44" s="76"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="76"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="58">
+        <v>0</v>
+      </c>
+      <c r="H44" s="57"/>
+      <c r="I44" s="58"/>
+      <c r="J44" s="57"/>
       <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
-      <c r="B45" s="77" t="s">
+      <c r="B45" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="78">
-        <v>0</v>
-      </c>
-      <c r="H45" s="79"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="80"/>
+      <c r="C45" s="62"/>
+      <c r="D45" s="62"/>
+      <c r="E45" s="62"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="63">
+        <v>0</v>
+      </c>
+      <c r="H45" s="64"/>
+      <c r="I45" s="65"/>
+      <c r="J45" s="66"/>
       <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="69" t="s">
+      <c r="B46" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="81">
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="56">
         <f>L40+G45</f>
         <v>116</v>
       </c>
-      <c r="H46" s="76"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="76"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="57"/>
       <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="81">
+      <c r="C47" s="55"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="56">
         <f>G43+G44-G46</f>
         <v>331</v>
       </c>
-      <c r="H47" s="76"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="76"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="58"/>
+      <c r="J47" s="57"/>
       <c r="K47" s="7"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="81">
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="56">
         <v>321</v>
       </c>
-      <c r="H48" s="76"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="76"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="58"/>
+      <c r="J48" s="57"/>
       <c r="K48" s="7"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="82">
+      <c r="C49" s="55"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="59">
         <f>G47-G48</f>
         <v>10</v>
       </c>
-      <c r="H49" s="83"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="83"/>
+      <c r="H49" s="60"/>
+      <c r="I49" s="61"/>
+      <c r="J49" s="60"/>
       <c r="K49" s="7"/>
       <c r="L49" s="2"/>
     </row>
@@ -2828,6 +2990,1269 @@
         <v>29</v>
       </c>
     </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+  </mergeCells>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC9BBAA-45FB-4076-A9CF-97F6C48F2A35}">
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="75" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+    </row>
+    <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="83" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="78"/>
+      <c r="B8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="84"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="46">
+        <v>1</v>
+      </c>
+      <c r="B9" s="43">
+        <v>1</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="85">
+        <v>1</v>
+      </c>
+      <c r="E9" s="34"/>
+      <c r="F9" s="13">
+        <f>SUM(B9:E9)</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="31">
+        <v>21</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="11">
+        <f>SUM(G9:J9)</f>
+        <v>21</v>
+      </c>
+      <c r="L9" s="5">
+        <f>SUM(F9+K9)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>2</v>
+      </c>
+      <c r="B10" s="40">
+        <v>5</v>
+      </c>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="13">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>5</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="11">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="47">
+        <v>3</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="19">
+        <v>11</v>
+      </c>
+      <c r="H11" s="38"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="11">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="47">
+        <v>4</v>
+      </c>
+      <c r="B12" s="40">
+        <v>3</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G12" s="32"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="47">
+        <v>5</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="38">
+        <v>1</v>
+      </c>
+      <c r="H13" s="38"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="47">
+        <v>6</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="47">
+        <v>7</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47">
+        <v>8</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="47">
+        <v>9</v>
+      </c>
+      <c r="B17" s="40">
+        <v>6</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="13">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G17" s="38">
+        <v>1</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47">
+        <v>10</v>
+      </c>
+      <c r="B18" s="40">
+        <v>1</v>
+      </c>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="47">
+        <v>11</v>
+      </c>
+      <c r="B19" s="40">
+        <v>2</v>
+      </c>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="47">
+        <v>12</v>
+      </c>
+      <c r="B20" s="40">
+        <v>2</v>
+      </c>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="47">
+        <v>13</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="47">
+        <v>14</v>
+      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="47">
+        <v>15</v>
+      </c>
+      <c r="B23" s="40">
+        <v>3</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L23" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="47">
+        <v>16</v>
+      </c>
+      <c r="B24" s="40">
+        <v>3</v>
+      </c>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G24" s="19">
+        <v>10</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="11">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L24" s="5">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="47">
+        <v>17</v>
+      </c>
+      <c r="B25" s="40">
+        <v>1</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G25" s="19">
+        <v>10</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14">
+        <v>1</v>
+      </c>
+      <c r="J25" s="14"/>
+      <c r="K25" s="11">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L25" s="5">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="47">
+        <v>18</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <v>10</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="11">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L26" s="5">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="47">
+        <v>19</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="11">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L27" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="47">
+        <v>20</v>
+      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="19"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="47">
+        <v>21</v>
+      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="19"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="47">
+        <v>22</v>
+      </c>
+      <c r="B30" s="40">
+        <v>5</v>
+      </c>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G30" s="19">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L30" s="5">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="47">
+        <v>23</v>
+      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="19"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="47">
+        <v>24</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="19"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="47">
+        <v>25</v>
+      </c>
+      <c r="B33" s="40">
+        <v>1</v>
+      </c>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="19"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="47">
+        <v>26</v>
+      </c>
+      <c r="B34" s="40">
+        <v>2</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="19"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="47">
+        <v>27</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="30"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="47">
+        <v>28</v>
+      </c>
+      <c r="B36" s="44"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="19"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="47">
+        <v>29</v>
+      </c>
+      <c r="B37" s="44"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="19"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="47">
+        <v>30</v>
+      </c>
+      <c r="B38" s="44"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="19"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="49">
+        <v>31</v>
+      </c>
+      <c r="B39" s="45"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="19"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48"/>
+      <c r="B40" s="52">
+        <f>SUM(B9:B39)</f>
+        <v>35</v>
+      </c>
+      <c r="C40" s="52">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="52">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E40" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="51">
+        <f>SUM(F9:F39)</f>
+        <v>36</v>
+      </c>
+      <c r="G40" s="12">
+        <f>SUM(G9:G39)</f>
+        <v>70</v>
+      </c>
+      <c r="H40" s="12">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="12">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="12">
+        <f t="shared" si="4"/>
+        <v>71</v>
+      </c>
+      <c r="L40" s="12">
+        <f t="shared" si="4"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="9"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="67"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="69"/>
+      <c r="I42" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="70"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="9"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="65">
+        <v>321</v>
+      </c>
+      <c r="H43" s="71"/>
+      <c r="I43" s="72"/>
+      <c r="J43" s="73"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="9"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="58">
+        <v>0</v>
+      </c>
+      <c r="H44" s="57"/>
+      <c r="I44" s="58"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="9"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="62"/>
+      <c r="D45" s="62"/>
+      <c r="E45" s="62"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="63">
+        <v>0</v>
+      </c>
+      <c r="H45" s="64"/>
+      <c r="I45" s="65"/>
+      <c r="J45" s="66"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="9"/>
+    </row>
+    <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="56">
+        <f>L40+G45</f>
+        <v>107</v>
+      </c>
+      <c r="H46" s="57"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="9"/>
+    </row>
+    <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="55"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="56">
+        <f>G43+G44-G46</f>
+        <v>214</v>
+      </c>
+      <c r="H47" s="57"/>
+      <c r="I47" s="58"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="56">
+        <v>214</v>
+      </c>
+      <c r="H48" s="57"/>
+      <c r="I48" s="58"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="55"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="59">
+        <f>G47-G48</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="60"/>
+      <c r="I49" s="61"/>
+      <c r="J49" s="60"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="23"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" s="28"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="B48:F48"/>

--- a/Gestion Stock 2026/BRH 2026/Fiche de Stock Global 2026.xlsx
+++ b/Gestion Stock 2026/BRH 2026/Fiche de Stock Global 2026.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\BRH 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DC0FB8-5554-4A70-A6B7-7E2E2A55E17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405738A8-A007-4C42-9BD7-50BA05B6D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="13" r:id="rId1"/>
     <sheet name="FEVRIER 2026" sheetId="14" r:id="rId2"/>
+    <sheet name="MARS 2026" sheetId="15" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="32">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -190,6 +191,30 @@
       <t>2026</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>Mois de MARS</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -923,7 +948,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1109,6 +1134,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1204,7 +1233,27 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1383,6 +1432,139 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF7AA404-A82D-450F-96D9-5810DB508A3B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5581650" y="7705725"/>
+          <a:ext cx="958850" cy="1257300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>473075</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8590667-C2B5-470A-9A4D-44E6C6F7CB9E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1791,58 +1973,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
+      <c r="A1" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
       <c r="E2" s="22"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="76" t="s">
+      <c r="G2" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
       <c r="E3" s="22"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
     </row>
     <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -1859,61 +2041,61 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="82" t="s">
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="83" t="s">
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="84" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="78"/>
+      <c r="A8" s="79"/>
       <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
@@ -1944,7 +2126,7 @@
       <c r="K8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="84"/>
+      <c r="L8" s="85"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
@@ -2819,149 +3001,149 @@
       <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="67"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="68" t="s">
+      <c r="A42" s="68"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="69"/>
-      <c r="I42" s="69" t="s">
+      <c r="H42" s="70"/>
+      <c r="I42" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="70"/>
+      <c r="J42" s="71"/>
       <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="65">
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="66">
         <v>447</v>
       </c>
-      <c r="H43" s="71"/>
-      <c r="I43" s="72"/>
-      <c r="J43" s="73"/>
+      <c r="H43" s="72"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="74"/>
       <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
-      <c r="B44" s="54" t="s">
+      <c r="B44" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="58">
-        <v>0</v>
-      </c>
-      <c r="H44" s="57"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="57"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="59">
+        <v>0</v>
+      </c>
+      <c r="H44" s="58"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="58"/>
       <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
-      <c r="B45" s="62" t="s">
+      <c r="B45" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="62"/>
-      <c r="D45" s="62"/>
-      <c r="E45" s="62"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="63">
-        <v>0</v>
-      </c>
-      <c r="H45" s="64"/>
-      <c r="I45" s="65"/>
-      <c r="J45" s="66"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="64">
+        <v>0</v>
+      </c>
+      <c r="H45" s="65"/>
+      <c r="I45" s="66"/>
+      <c r="J45" s="67"/>
       <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="54" t="s">
+      <c r="B46" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="56">
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="57">
         <f>L40+G45</f>
         <v>116</v>
       </c>
-      <c r="H46" s="57"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="57"/>
+      <c r="H46" s="58"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="58"/>
       <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
-      <c r="B47" s="54" t="s">
+      <c r="B47" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="55"/>
-      <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="55"/>
-      <c r="G47" s="56">
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="57">
         <f>G43+G44-G46</f>
         <v>331</v>
       </c>
-      <c r="H47" s="57"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="57"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="58"/>
       <c r="K47" s="7"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="54" t="s">
+      <c r="B48" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="55"/>
-      <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="56">
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="57">
         <v>321</v>
       </c>
-      <c r="H48" s="57"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="57"/>
+      <c r="H48" s="58"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="58"/>
       <c r="K48" s="7"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
-      <c r="B49" s="54" t="s">
+      <c r="B49" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="55"/>
-      <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="59">
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="60">
         <f>G47-G48</f>
         <v>10</v>
       </c>
-      <c r="H49" s="60"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="60"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="62"/>
+      <c r="J49" s="61"/>
       <c r="K49" s="7"/>
       <c r="L49" s="2"/>
     </row>
@@ -2990,6 +3172,1269 @@
         <v>29</v>
       </c>
     </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:L3"/>
+  </mergeCells>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC9BBAA-45FB-4076-A9CF-97F6C48F2A35}">
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="76" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="77" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="77" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+    </row>
+    <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="78" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="83" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="84" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="79"/>
+      <c r="B8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="85"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="46">
+        <v>1</v>
+      </c>
+      <c r="B9" s="43">
+        <v>1</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="54">
+        <v>1</v>
+      </c>
+      <c r="E9" s="34"/>
+      <c r="F9" s="13">
+        <f>SUM(B9:E9)</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="31">
+        <v>21</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="11">
+        <f>SUM(G9:J9)</f>
+        <v>21</v>
+      </c>
+      <c r="L9" s="5">
+        <f>SUM(F9+K9)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>2</v>
+      </c>
+      <c r="B10" s="40">
+        <v>5</v>
+      </c>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="13">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>5</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="11">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="47">
+        <v>3</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="19">
+        <v>11</v>
+      </c>
+      <c r="H11" s="38"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="11">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="47">
+        <v>4</v>
+      </c>
+      <c r="B12" s="40">
+        <v>3</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G12" s="32"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="47">
+        <v>5</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="38">
+        <v>1</v>
+      </c>
+      <c r="H13" s="38"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="47">
+        <v>6</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="47">
+        <v>7</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47">
+        <v>8</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="47">
+        <v>9</v>
+      </c>
+      <c r="B17" s="40">
+        <v>6</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="13">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G17" s="38">
+        <v>1</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47">
+        <v>10</v>
+      </c>
+      <c r="B18" s="40">
+        <v>1</v>
+      </c>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="47">
+        <v>11</v>
+      </c>
+      <c r="B19" s="40">
+        <v>2</v>
+      </c>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="47">
+        <v>12</v>
+      </c>
+      <c r="B20" s="40">
+        <v>2</v>
+      </c>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="47">
+        <v>13</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="47">
+        <v>14</v>
+      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="47">
+        <v>15</v>
+      </c>
+      <c r="B23" s="40">
+        <v>3</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L23" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="47">
+        <v>16</v>
+      </c>
+      <c r="B24" s="40">
+        <v>3</v>
+      </c>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G24" s="19">
+        <v>10</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="11">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L24" s="5">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="47">
+        <v>17</v>
+      </c>
+      <c r="B25" s="40">
+        <v>1</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G25" s="19">
+        <v>10</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14">
+        <v>1</v>
+      </c>
+      <c r="J25" s="14"/>
+      <c r="K25" s="11">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L25" s="5">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="47">
+        <v>18</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <v>10</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="11">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L26" s="5">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="47">
+        <v>19</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="11">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L27" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="47">
+        <v>20</v>
+      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="19"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="47">
+        <v>21</v>
+      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="19"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="47">
+        <v>22</v>
+      </c>
+      <c r="B30" s="40">
+        <v>5</v>
+      </c>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G30" s="19">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L30" s="5">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="47">
+        <v>23</v>
+      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="19"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="47">
+        <v>24</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="19"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="47">
+        <v>25</v>
+      </c>
+      <c r="B33" s="40">
+        <v>1</v>
+      </c>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="19"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="47">
+        <v>26</v>
+      </c>
+      <c r="B34" s="40">
+        <v>2</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="19"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="47">
+        <v>27</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="30"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="47">
+        <v>28</v>
+      </c>
+      <c r="B36" s="44"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="19"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="47">
+        <v>29</v>
+      </c>
+      <c r="B37" s="44"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="19"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="47">
+        <v>30</v>
+      </c>
+      <c r="B38" s="44"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="19"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="49">
+        <v>31</v>
+      </c>
+      <c r="B39" s="45"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="19"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48"/>
+      <c r="B40" s="52">
+        <f>SUM(B9:B39)</f>
+        <v>35</v>
+      </c>
+      <c r="C40" s="52">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="52">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E40" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="51">
+        <f>SUM(F9:F39)</f>
+        <v>36</v>
+      </c>
+      <c r="G40" s="12">
+        <f>SUM(G9:G39)</f>
+        <v>70</v>
+      </c>
+      <c r="H40" s="12">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="12">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="12">
+        <f t="shared" si="4"/>
+        <v>71</v>
+      </c>
+      <c r="L40" s="12">
+        <f t="shared" si="4"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="9"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="68"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="71"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="9"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="66">
+        <v>321</v>
+      </c>
+      <c r="H43" s="72"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="74"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="9"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="59">
+        <v>0</v>
+      </c>
+      <c r="H44" s="58"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="58"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="9"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="63" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="64">
+        <v>0</v>
+      </c>
+      <c r="H45" s="65"/>
+      <c r="I45" s="66"/>
+      <c r="J45" s="67"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="9"/>
+    </row>
+    <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="57">
+        <f>L40+G45</f>
+        <v>107</v>
+      </c>
+      <c r="H46" s="58"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="58"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="9"/>
+    </row>
+    <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="57">
+        <f>G43+G44-G46</f>
+        <v>214</v>
+      </c>
+      <c r="H47" s="58"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="58"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="57">
+        <v>214</v>
+      </c>
+      <c r="H48" s="58"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="58"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="60">
+        <f>G47-G48</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="61"/>
+      <c r="I49" s="62"/>
+      <c r="J49" s="61"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="23"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" s="28"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="A1:D1"/>
@@ -3035,8 +4480,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC9BBAA-45FB-4076-A9CF-97F6C48F2A35}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F79BFF48-00BC-419E-8391-D515B4A2FE9A}">
   <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3045,58 +4490,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
+      <c r="A1" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
       <c r="E2" s="22"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="76" t="s">
+      <c r="G2" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
       <c r="E3" s="22"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="76" t="s">
+      <c r="G3" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
     </row>
     <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -3113,61 +4558,61 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
+      <c r="A6" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="82" t="s">
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="83" t="s">
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="84" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="78"/>
+      <c r="A8" s="79"/>
       <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
@@ -3198,7 +4643,7 @@
       <c r="K8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="84"/>
+      <c r="L8" s="85"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
@@ -3207,28 +4652,28 @@
       <c r="B9" s="43">
         <v>1</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="85">
-        <v>1</v>
-      </c>
-      <c r="E9" s="34"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="87"/>
       <c r="F9" s="13">
         <f>SUM(B9:E9)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="31">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H9" s="35"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
+      <c r="I9" s="86">
+        <v>1</v>
+      </c>
+      <c r="J9" s="86"/>
       <c r="K9" s="11">
         <f>SUM(G9:J9)</f>
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L9" s="5">
         <f>SUM(F9+K9)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3236,53 +4681,55 @@
         <v>2</v>
       </c>
       <c r="B10" s="40">
-        <v>5</v>
-      </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="37"/>
+        <v>1</v>
+      </c>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="39"/>
       <c r="F10" s="13">
         <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
-        <v>5</v>
-      </c>
-      <c r="G10" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="19">
+        <v>1</v>
+      </c>
       <c r="H10" s="38"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
       <c r="K10" s="11">
         <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>3</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
+      <c r="B11" s="40">
+        <v>5</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="39"/>
       <c r="F11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="19">
-        <v>11</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G11" s="19"/>
       <c r="H11" s="38"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
       <c r="K11" s="11">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3290,22 +4737,24 @@
         <v>4</v>
       </c>
       <c r="B12" s="40">
-        <v>3</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="37"/>
+        <v>1</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="39"/>
       <c r="F12" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G12" s="32"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="32">
+        <v>2</v>
+      </c>
       <c r="H12" s="38"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
       <c r="K12" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="2"/>
@@ -3317,26 +4766,26 @@
         <v>5</v>
       </c>
       <c r="B13" s="40"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="39"/>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G13" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="38"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
       <c r="K13" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3344,17 +4793,17 @@
         <v>6</v>
       </c>
       <c r="B14" s="40"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="37"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="39"/>
       <c r="F14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G14" s="38"/>
       <c r="H14" s="38"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
       <c r="K14" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3369,8 +4818,8 @@
         <v>7</v>
       </c>
       <c r="B15" s="40"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="39"/>
       <c r="F15" s="13">
         <f t="shared" si="0"/>
@@ -3378,8 +4827,8 @@
       </c>
       <c r="G15" s="38"/>
       <c r="H15" s="38"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3394,17 +4843,17 @@
         <v>8</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="37"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="39"/>
       <c r="F16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="38"/>
       <c r="H16" s="38"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
       <c r="K16" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3418,29 +4867,25 @@
       <c r="A17" s="47">
         <v>9</v>
       </c>
-      <c r="B17" s="40">
-        <v>6</v>
-      </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="37"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="39"/>
       <c r="F17" s="13">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="G17" s="38">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G17" s="38"/>
       <c r="H17" s="38"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
       <c r="K17" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3448,80 +4893,76 @@
         <v>10</v>
       </c>
       <c r="B18" s="40">
-        <v>1</v>
-      </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="37"/>
+        <v>10</v>
+      </c>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="39"/>
       <c r="F18" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G18" s="40"/>
       <c r="H18" s="40"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
       <c r="K18" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="47">
         <v>11</v>
       </c>
-      <c r="B19" s="40">
-        <v>2</v>
-      </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="37"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="39"/>
       <c r="F19" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="38"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
       <c r="K19" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>12</v>
       </c>
-      <c r="B20" s="40">
-        <v>2</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="37"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="39"/>
       <c r="F20" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="19"/>
       <c r="H20" s="38"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="88"/>
       <c r="K20" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3529,17 +4970,17 @@
         <v>13</v>
       </c>
       <c r="B21" s="40"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="37"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="39"/>
       <c r="F21" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="41"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
       <c r="K21" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3554,17 +4995,17 @@
         <v>14</v>
       </c>
       <c r="B22" s="40"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="39"/>
       <c r="F22" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G22" s="21"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
       <c r="K22" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3578,29 +5019,27 @@
       <c r="A23" s="47">
         <v>15</v>
       </c>
-      <c r="B23" s="40">
-        <v>3</v>
-      </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="39"/>
       <c r="F23" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G23" s="19">
         <v>1</v>
       </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
       <c r="K23" s="11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3610,57 +5049,51 @@
       <c r="B24" s="40">
         <v>3</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="37"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="39"/>
       <c r="F24" s="13">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G24" s="19">
-        <v>10</v>
-      </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
       <c r="K24" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="47">
         <v>17</v>
       </c>
-      <c r="B25" s="40">
-        <v>1</v>
-      </c>
+      <c r="B25" s="40"/>
       <c r="C25" s="40"/>
       <c r="D25" s="42"/>
-      <c r="E25" s="37"/>
+      <c r="E25" s="39"/>
       <c r="F25" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G25" s="19">
-        <v>10</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14">
-        <v>1</v>
-      </c>
-      <c r="J25" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="19"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
       <c r="K25" s="11">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3668,53 +5101,51 @@
         <v>18</v>
       </c>
       <c r="B26" s="40"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="37"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="39"/>
       <c r="F26" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G26" s="19">
-        <v>10</v>
-      </c>
+      <c r="G26" s="19"/>
       <c r="H26" s="53"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
       <c r="K26" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="47">
         <v>19</v>
       </c>
-      <c r="B27" s="40"/>
+      <c r="B27" s="40">
+        <v>1</v>
+      </c>
       <c r="C27" s="42"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="39"/>
       <c r="F27" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="19">
-        <v>4</v>
-      </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="G27" s="19"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
       <c r="K27" s="11">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3722,17 +5153,17 @@
         <v>20</v>
       </c>
       <c r="B28" s="40"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="37"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="39"/>
       <c r="F28" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G28" s="19"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
       <c r="K28" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3747,17 +5178,17 @@
         <v>21</v>
       </c>
       <c r="B29" s="40"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="37"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="39"/>
       <c r="F29" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G29" s="19"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
       <c r="K29" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3771,54 +5202,52 @@
       <c r="A30" s="47">
         <v>22</v>
       </c>
-      <c r="B30" s="40">
-        <v>5</v>
-      </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="39"/>
       <c r="F30" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G30" s="19">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="19"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
       <c r="K30" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="47">
         <v>23</v>
       </c>
-      <c r="B31" s="40"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37"/>
+      <c r="B31" s="40">
+        <v>3</v>
+      </c>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="39"/>
       <c r="F31" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="19"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
       <c r="K31" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3826,17 +5255,17 @@
         <v>24</v>
       </c>
       <c r="B32" s="40"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="37"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="39"/>
       <c r="F32" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G32" s="19"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
       <c r="K32" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3851,26 +5280,26 @@
         <v>25</v>
       </c>
       <c r="B33" s="40">
-        <v>1</v>
-      </c>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="37"/>
+        <v>2</v>
+      </c>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="39"/>
       <c r="F33" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="19"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
       <c r="K33" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3878,26 +5307,30 @@
         <v>26</v>
       </c>
       <c r="B34" s="40">
+        <v>1</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42">
         <v>2</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="37"/>
+      <c r="E34" s="39"/>
       <c r="F34" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G34" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="G34" s="19">
+        <v>1</v>
+      </c>
       <c r="H34" s="38"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
       <c r="K34" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3905,17 +5338,17 @@
         <v>27</v>
       </c>
       <c r="B35" s="44"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="37"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="39"/>
       <c r="F35" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G35" s="30"/>
       <c r="H35" s="38"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
       <c r="K35" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3930,17 +5363,17 @@
         <v>28</v>
       </c>
       <c r="B36" s="44"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="15"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="89"/>
       <c r="F36" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G36" s="19"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
       <c r="K36" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3955,24 +5388,26 @@
         <v>29</v>
       </c>
       <c r="B37" s="44"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="15"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53">
+        <v>1</v>
+      </c>
+      <c r="E37" s="89"/>
       <c r="F37" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="19"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
       <c r="K37" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3980,17 +5415,17 @@
         <v>30</v>
       </c>
       <c r="B38" s="44"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="15"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="89"/>
       <c r="F38" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G38" s="19"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
       <c r="K38" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4004,32 +5439,36 @@
       <c r="A39" s="49">
         <v>31</v>
       </c>
-      <c r="B39" s="45"/>
-      <c r="C39" s="16"/>
+      <c r="B39" s="45">
+        <v>3</v>
+      </c>
+      <c r="C39" s="90"/>
       <c r="D39" s="45"/>
-      <c r="E39" s="17"/>
+      <c r="E39" s="91"/>
       <c r="F39" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="19"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
+        <v>3</v>
+      </c>
+      <c r="G39" s="19">
+        <v>1</v>
+      </c>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
       <c r="K39" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="48"/>
       <c r="B40" s="52">
         <f>SUM(B9:B39)</f>
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C40" s="52">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -4037,7 +5476,7 @@
       </c>
       <c r="D40" s="52">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="52">
         <f t="shared" si="3"/>
@@ -4045,11 +5484,11 @@
       </c>
       <c r="F40" s="51">
         <f>SUM(F9:F39)</f>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G40" s="12">
         <f>SUM(G9:G39)</f>
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
@@ -4065,11 +5504,11 @@
       </c>
       <c r="K40" s="12">
         <f t="shared" si="4"/>
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="4"/>
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4087,149 +5526,149 @@
       <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="67"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="68" t="s">
+      <c r="A42" s="68"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="69"/>
-      <c r="I42" s="69" t="s">
+      <c r="H42" s="70"/>
+      <c r="I42" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="70"/>
+      <c r="J42" s="71"/>
       <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="65">
-        <v>321</v>
-      </c>
-      <c r="H43" s="71"/>
-      <c r="I43" s="72"/>
-      <c r="J43" s="73"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="66">
+        <v>214</v>
+      </c>
+      <c r="H43" s="72"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="74"/>
       <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
-      <c r="B44" s="54" t="s">
+      <c r="B44" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="58">
-        <v>0</v>
-      </c>
-      <c r="H44" s="57"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="57"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="59">
+        <v>0</v>
+      </c>
+      <c r="H44" s="58"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="58"/>
       <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
-      <c r="B45" s="62" t="s">
+      <c r="B45" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="62"/>
-      <c r="D45" s="62"/>
-      <c r="E45" s="62"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="63">
-        <v>0</v>
-      </c>
-      <c r="H45" s="64"/>
-      <c r="I45" s="65"/>
-      <c r="J45" s="66"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="64">
+        <v>0</v>
+      </c>
+      <c r="H45" s="65"/>
+      <c r="I45" s="66"/>
+      <c r="J45" s="67"/>
       <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="54" t="s">
+      <c r="B46" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="56">
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="57">
         <f>L40+G45</f>
-        <v>107</v>
-      </c>
-      <c r="H46" s="57"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="57"/>
+        <v>45</v>
+      </c>
+      <c r="H46" s="58"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="58"/>
       <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
-      <c r="B47" s="54" t="s">
+      <c r="B47" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="55"/>
-      <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="55"/>
-      <c r="G47" s="56">
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="57">
         <f>G43+G44-G46</f>
-        <v>214</v>
-      </c>
-      <c r="H47" s="57"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="57"/>
+        <v>169</v>
+      </c>
+      <c r="H47" s="58"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="58"/>
       <c r="K47" s="7"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="54" t="s">
+      <c r="B48" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="55"/>
-      <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="56">
-        <v>214</v>
-      </c>
-      <c r="H48" s="57"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="57"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="57">
+        <v>169</v>
+      </c>
+      <c r="H48" s="58"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="58"/>
       <c r="K48" s="7"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
-      <c r="B49" s="54" t="s">
+      <c r="B49" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="55"/>
-      <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="59">
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="60">
         <f>G47-G48</f>
         <v>0</v>
       </c>
-      <c r="H49" s="60"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="60"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="62"/>
+      <c r="J49" s="61"/>
       <c r="K49" s="7"/>
       <c r="L49" s="2"/>
     </row>

--- a/Gestion Stock 2026/BRH 2026/Fiche de Stock Global 2026.xlsx
+++ b/Gestion Stock 2026/BRH 2026/Fiche de Stock Global 2026.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\BRH 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405738A8-A007-4C42-9BD7-50BA05B6D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B708AF-B91D-46D2-8537-FDB8F744F3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="13" r:id="rId1"/>
     <sheet name="FEVRIER 2026" sheetId="14" r:id="rId2"/>
     <sheet name="MARS 2026" sheetId="15" r:id="rId3"/>
+    <sheet name="AVRIL 2026" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="34">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -215,6 +216,33 @@
       <t>2026</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>Mois de AVRIL</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>1 Compteurs DN 30 Destination Agence Beni Slimane</t>
+  </si>
 </sst>
 </file>
 
@@ -1138,6 +1166,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1232,30 +1284,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1677,6 +1705,139 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>473075</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{776724E3-7329-4688-BCDB-A16BFE5C1E4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5581650" y="7705725"/>
+          <a:ext cx="958850" cy="1257300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -1973,58 +2134,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
+      <c r="A1" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
-      <c r="G1" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
+      <c r="G1" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
       <c r="E2" s="22"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="77" t="s">
+      <c r="G2" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
       <c r="E3" s="22"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="77" t="s">
+      <c r="G3" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -2041,61 +2202,61 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="83" t="s">
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="84" t="s">
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="90" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="79"/>
+      <c r="A8" s="85"/>
       <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
@@ -2126,7 +2287,7 @@
       <c r="K8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="85"/>
+      <c r="L8" s="91"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
@@ -3001,149 +3162,149 @@
       <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="68"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="69" t="s">
+      <c r="A42" s="74"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70" t="s">
+      <c r="H42" s="76"/>
+      <c r="I42" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="71"/>
+      <c r="J42" s="77"/>
       <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
-      <c r="B43" s="55" t="s">
+      <c r="B43" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="66">
+      <c r="C43" s="62"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="62"/>
+      <c r="G43" s="72">
         <v>447</v>
       </c>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="74"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="80"/>
       <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
-      <c r="B44" s="55" t="s">
+      <c r="B44" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="56"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="59">
-        <v>0</v>
-      </c>
-      <c r="H44" s="58"/>
-      <c r="I44" s="59"/>
-      <c r="J44" s="58"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="65">
+        <v>0</v>
+      </c>
+      <c r="H44" s="64"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="64"/>
       <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="63"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="63"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="64">
-        <v>0</v>
-      </c>
-      <c r="H45" s="65"/>
-      <c r="I45" s="66"/>
-      <c r="J45" s="67"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="70">
+        <v>0</v>
+      </c>
+      <c r="H45" s="71"/>
+      <c r="I45" s="72"/>
+      <c r="J45" s="73"/>
       <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="55" t="s">
+      <c r="B46" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="57">
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="63">
         <f>L40+G45</f>
         <v>116</v>
       </c>
-      <c r="H46" s="58"/>
-      <c r="I46" s="59"/>
-      <c r="J46" s="58"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="64"/>
       <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
-      <c r="B47" s="55" t="s">
+      <c r="B47" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="56"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="57">
+      <c r="C47" s="62"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="62"/>
+      <c r="G47" s="63">
         <f>G43+G44-G46</f>
         <v>331</v>
       </c>
-      <c r="H47" s="58"/>
-      <c r="I47" s="59"/>
-      <c r="J47" s="58"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="64"/>
       <c r="K47" s="7"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="55" t="s">
+      <c r="B48" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="56"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="56"/>
-      <c r="G48" s="57">
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="63">
         <v>321</v>
       </c>
-      <c r="H48" s="58"/>
-      <c r="I48" s="59"/>
-      <c r="J48" s="58"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="64"/>
       <c r="K48" s="7"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
-      <c r="B49" s="55" t="s">
+      <c r="B49" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="56"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="60">
+      <c r="C49" s="62"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="62"/>
+      <c r="G49" s="66">
         <f>G47-G48</f>
         <v>10</v>
       </c>
-      <c r="H49" s="61"/>
-      <c r="I49" s="62"/>
-      <c r="J49" s="61"/>
+      <c r="H49" s="67"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="67"/>
       <c r="K49" s="7"/>
       <c r="L49" s="2"/>
     </row>
@@ -3227,58 +3388,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
+      <c r="A1" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
-      <c r="G1" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
+      <c r="G1" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
       <c r="E2" s="22"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="77" t="s">
+      <c r="G2" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
       <c r="E3" s="22"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="77" t="s">
+      <c r="G3" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -3295,61 +3456,61 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="83" t="s">
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="84" t="s">
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="90" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="79"/>
+      <c r="A8" s="85"/>
       <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
@@ -3380,7 +3541,7 @@
       <c r="K8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="85"/>
+      <c r="L8" s="91"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
@@ -4269,149 +4430,149 @@
       <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="68"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="69" t="s">
+      <c r="A42" s="74"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70" t="s">
+      <c r="H42" s="76"/>
+      <c r="I42" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="71"/>
+      <c r="J42" s="77"/>
       <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
-      <c r="B43" s="55" t="s">
+      <c r="B43" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="66">
+      <c r="C43" s="62"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="62"/>
+      <c r="G43" s="72">
         <v>321</v>
       </c>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="74"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="80"/>
       <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
-      <c r="B44" s="55" t="s">
+      <c r="B44" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="56"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="59">
-        <v>0</v>
-      </c>
-      <c r="H44" s="58"/>
-      <c r="I44" s="59"/>
-      <c r="J44" s="58"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="65">
+        <v>0</v>
+      </c>
+      <c r="H44" s="64"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="64"/>
       <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="63"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="63"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="64">
-        <v>0</v>
-      </c>
-      <c r="H45" s="65"/>
-      <c r="I45" s="66"/>
-      <c r="J45" s="67"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="70">
+        <v>0</v>
+      </c>
+      <c r="H45" s="71"/>
+      <c r="I45" s="72"/>
+      <c r="J45" s="73"/>
       <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="55" t="s">
+      <c r="B46" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="57">
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="63">
         <f>L40+G45</f>
         <v>107</v>
       </c>
-      <c r="H46" s="58"/>
-      <c r="I46" s="59"/>
-      <c r="J46" s="58"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="64"/>
       <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
-      <c r="B47" s="55" t="s">
+      <c r="B47" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="56"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="57">
+      <c r="C47" s="62"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="62"/>
+      <c r="G47" s="63">
         <f>G43+G44-G46</f>
         <v>214</v>
       </c>
-      <c r="H47" s="58"/>
-      <c r="I47" s="59"/>
-      <c r="J47" s="58"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="64"/>
       <c r="K47" s="7"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="55" t="s">
+      <c r="B48" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="56"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="56"/>
-      <c r="G48" s="57">
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="63">
         <v>214</v>
       </c>
-      <c r="H48" s="58"/>
-      <c r="I48" s="59"/>
-      <c r="J48" s="58"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="64"/>
       <c r="K48" s="7"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
-      <c r="B49" s="55" t="s">
+      <c r="B49" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="56"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="60">
+      <c r="C49" s="62"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="62"/>
+      <c r="G49" s="66">
         <f>G47-G48</f>
         <v>0</v>
       </c>
-      <c r="H49" s="61"/>
-      <c r="I49" s="62"/>
-      <c r="J49" s="61"/>
+      <c r="H49" s="67"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="67"/>
       <c r="K49" s="7"/>
       <c r="L49" s="2"/>
     </row>
@@ -4490,58 +4651,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
+      <c r="A1" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
-      <c r="G1" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
+      <c r="G1" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
       <c r="E2" s="22"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="77" t="s">
+      <c r="G2" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
       <c r="E3" s="22"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="77" t="s">
+      <c r="G3" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
     </row>
     <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -4558,61 +4719,61 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="83" t="s">
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="84" t="s">
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="90" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="79"/>
+      <c r="A8" s="85"/>
       <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
@@ -4643,7 +4804,7 @@
       <c r="K8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="85"/>
+      <c r="L8" s="91"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
@@ -4654,7 +4815,7 @@
       </c>
       <c r="C9" s="54"/>
       <c r="D9" s="54"/>
-      <c r="E9" s="87"/>
+      <c r="E9" s="56"/>
       <c r="F9" s="13">
         <f>SUM(B9:E9)</f>
         <v>1</v>
@@ -4663,10 +4824,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="35"/>
-      <c r="I9" s="86">
-        <v>1</v>
-      </c>
-      <c r="J9" s="86"/>
+      <c r="I9" s="55">
+        <v>1</v>
+      </c>
+      <c r="J9" s="55"/>
       <c r="K9" s="11">
         <f>SUM(G9:J9)</f>
         <v>2</v>
@@ -4954,8 +5115,8 @@
       </c>
       <c r="G20" s="19"/>
       <c r="H20" s="38"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="88"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
       <c r="K20" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -5365,7 +5526,7 @@
       <c r="B36" s="44"/>
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
-      <c r="E36" s="89"/>
+      <c r="E36" s="58"/>
       <c r="F36" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5392,7 +5553,7 @@
       <c r="D37" s="53">
         <v>1</v>
       </c>
-      <c r="E37" s="89"/>
+      <c r="E37" s="58"/>
       <c r="F37" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -5417,7 +5578,7 @@
       <c r="B38" s="44"/>
       <c r="C38" s="53"/>
       <c r="D38" s="53"/>
-      <c r="E38" s="89"/>
+      <c r="E38" s="58"/>
       <c r="F38" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5442,9 +5603,9 @@
       <c r="B39" s="45">
         <v>3</v>
       </c>
-      <c r="C39" s="90"/>
+      <c r="C39" s="59"/>
       <c r="D39" s="45"/>
-      <c r="E39" s="91"/>
+      <c r="E39" s="60"/>
       <c r="F39" s="13">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -5526,149 +5687,149 @@
       <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="68"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="69" t="s">
+      <c r="A42" s="74"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70" t="s">
+      <c r="H42" s="76"/>
+      <c r="I42" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="71"/>
+      <c r="J42" s="77"/>
       <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
-      <c r="B43" s="55" t="s">
+      <c r="B43" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="66">
+      <c r="C43" s="62"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="62"/>
+      <c r="G43" s="72">
         <v>214</v>
       </c>
-      <c r="H43" s="72"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="74"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="80"/>
       <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
-      <c r="B44" s="55" t="s">
+      <c r="B44" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="56"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="59">
-        <v>0</v>
-      </c>
-      <c r="H44" s="58"/>
-      <c r="I44" s="59"/>
-      <c r="J44" s="58"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="65">
+        <v>0</v>
+      </c>
+      <c r="H44" s="64"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="64"/>
       <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="63"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="63"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="64">
-        <v>0</v>
-      </c>
-      <c r="H45" s="65"/>
-      <c r="I45" s="66"/>
-      <c r="J45" s="67"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="70">
+        <v>0</v>
+      </c>
+      <c r="H45" s="71"/>
+      <c r="I45" s="72"/>
+      <c r="J45" s="73"/>
       <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="55" t="s">
+      <c r="B46" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="57">
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="63">
         <f>L40+G45</f>
         <v>45</v>
       </c>
-      <c r="H46" s="58"/>
-      <c r="I46" s="59"/>
-      <c r="J46" s="58"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="64"/>
       <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
-      <c r="B47" s="55" t="s">
+      <c r="B47" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="56"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="57">
+      <c r="C47" s="62"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="62"/>
+      <c r="G47" s="63">
         <f>G43+G44-G46</f>
         <v>169</v>
       </c>
-      <c r="H47" s="58"/>
-      <c r="I47" s="59"/>
-      <c r="J47" s="58"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="64"/>
       <c r="K47" s="7"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="55" t="s">
+      <c r="B48" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="56"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="56"/>
-      <c r="G48" s="57">
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="63">
         <v>169</v>
       </c>
-      <c r="H48" s="58"/>
-      <c r="I48" s="59"/>
-      <c r="J48" s="58"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="64"/>
       <c r="K48" s="7"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
-      <c r="B49" s="55" t="s">
+      <c r="B49" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="56"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="60">
+      <c r="C49" s="62"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="62"/>
+      <c r="G49" s="66">
         <f>G47-G48</f>
         <v>0</v>
       </c>
-      <c r="H49" s="61"/>
-      <c r="I49" s="62"/>
-      <c r="J49" s="61"/>
+      <c r="H49" s="67"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="67"/>
       <c r="K49" s="7"/>
       <c r="L49" s="2"/>
     </row>
@@ -5735,4 +5896,1280 @@
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6601AF8D-E42B-49F4-9FB8-5130A136BA40}">
+  <dimension ref="A1:L53"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="82" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="83" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="83" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+    </row>
+    <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="81" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="82" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="84" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="90" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="85"/>
+      <c r="B8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="91"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="46">
+        <v>1</v>
+      </c>
+      <c r="B9" s="43">
+        <v>3</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="13">
+        <f>SUM(B9:E9)</f>
+        <v>3</v>
+      </c>
+      <c r="G9" s="31"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="11">
+        <f>SUM(G9:J9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <f>SUM(F9+K9)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>2</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="13">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="11">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="47">
+        <v>3</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="47">
+        <v>4</v>
+      </c>
+      <c r="B12" s="40"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="32"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="47">
+        <v>5</v>
+      </c>
+      <c r="B13" s="40">
+        <v>2</v>
+      </c>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G13" s="38">
+        <v>3</v>
+      </c>
+      <c r="H13" s="38"/>
+      <c r="I13" s="53">
+        <v>1</v>
+      </c>
+      <c r="J13" s="53"/>
+      <c r="K13" s="11">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="47">
+        <v>6</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="47">
+        <v>7</v>
+      </c>
+      <c r="B15" s="40">
+        <v>5</v>
+      </c>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G15" s="38">
+        <v>7</v>
+      </c>
+      <c r="H15" s="38"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="11">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47">
+        <v>8</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="38">
+        <v>12</v>
+      </c>
+      <c r="H16" s="38">
+        <v>1</v>
+      </c>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="11">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="47">
+        <v>9</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47">
+        <v>10</v>
+      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="47">
+        <v>11</v>
+      </c>
+      <c r="B19" s="40"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="47">
+        <v>12</v>
+      </c>
+      <c r="B20" s="40">
+        <v>2</v>
+      </c>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42">
+        <v>2</v>
+      </c>
+      <c r="E20" s="39"/>
+      <c r="F20" s="13">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="47">
+        <v>13</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="21">
+        <v>2</v>
+      </c>
+      <c r="H21" s="41"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="11">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="47">
+        <v>14</v>
+      </c>
+      <c r="B22" s="40">
+        <v>1</v>
+      </c>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="47">
+        <v>15</v>
+      </c>
+      <c r="B23" s="40">
+        <v>2</v>
+      </c>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1</v>
+      </c>
+      <c r="H23" s="53">
+        <v>1</v>
+      </c>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="11">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L23" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="47">
+        <v>16</v>
+      </c>
+      <c r="B24" s="40">
+        <v>2</v>
+      </c>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="47">
+        <v>17</v>
+      </c>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="19"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="47">
+        <v>18</v>
+      </c>
+      <c r="B26" s="40">
+        <v>2</v>
+      </c>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G26" s="19"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53">
+        <v>1</v>
+      </c>
+      <c r="J26" s="53"/>
+      <c r="K26" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L26" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="47">
+        <v>19</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="19"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="47">
+        <v>20</v>
+      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="19"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="47">
+        <v>21</v>
+      </c>
+      <c r="B29" s="40">
+        <v>1</v>
+      </c>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G29" s="19">
+        <v>9</v>
+      </c>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="11">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="L29" s="5">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="47">
+        <v>22</v>
+      </c>
+      <c r="B30" s="40">
+        <v>6</v>
+      </c>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="13">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G30" s="19"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="47">
+        <v>23</v>
+      </c>
+      <c r="B31" s="40">
+        <v>1</v>
+      </c>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G31" s="19"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="47">
+        <v>24</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="19"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="47">
+        <v>25</v>
+      </c>
+      <c r="B33" s="40"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="19">
+        <v>10</v>
+      </c>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="11">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L33" s="5">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="47">
+        <v>26</v>
+      </c>
+      <c r="B34" s="40">
+        <v>4</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="13">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G34" s="19"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="47">
+        <v>27</v>
+      </c>
+      <c r="B35" s="44">
+        <v>1</v>
+      </c>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G35" s="30"/>
+      <c r="H35" s="38">
+        <v>1</v>
+      </c>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L35" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="47">
+        <v>28</v>
+      </c>
+      <c r="B36" s="44">
+        <v>3</v>
+      </c>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G36" s="19"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="47">
+        <v>29</v>
+      </c>
+      <c r="B37" s="44"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="19">
+        <v>3</v>
+      </c>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="11">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L37" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="47">
+        <v>30</v>
+      </c>
+      <c r="B38" s="44">
+        <v>2</v>
+      </c>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G38" s="19"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="49">
+        <v>31</v>
+      </c>
+      <c r="B39" s="45"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="19"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48"/>
+      <c r="B40" s="52">
+        <f>SUM(B9:B39)</f>
+        <v>37</v>
+      </c>
+      <c r="C40" s="52">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="52">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="E40" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="51">
+        <f>SUM(F9:F39)</f>
+        <v>39</v>
+      </c>
+      <c r="G40" s="12">
+        <f>SUM(G9:G39)</f>
+        <v>47</v>
+      </c>
+      <c r="H40" s="12">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>3</v>
+      </c>
+      <c r="I40" s="12">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J40" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="12">
+        <f t="shared" si="4"/>
+        <v>52</v>
+      </c>
+      <c r="L40" s="12">
+        <f t="shared" si="4"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="9"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="74"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="75" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="76"/>
+      <c r="I42" s="76" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="77"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="9"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="62"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="62"/>
+      <c r="G43" s="72">
+        <v>169</v>
+      </c>
+      <c r="H43" s="78"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="80"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="9"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="62"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="65">
+        <v>1</v>
+      </c>
+      <c r="H44" s="64"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="64"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="9"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="70">
+        <v>0</v>
+      </c>
+      <c r="H45" s="71"/>
+      <c r="I45" s="72"/>
+      <c r="J45" s="73"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="9"/>
+    </row>
+    <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="63">
+        <f>L40+G45</f>
+        <v>91</v>
+      </c>
+      <c r="H46" s="64"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="64"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="9"/>
+    </row>
+    <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="62"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="62"/>
+      <c r="G47" s="63">
+        <f>G43+G44-G46</f>
+        <v>79</v>
+      </c>
+      <c r="H47" s="64"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="64"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="63">
+        <v>78</v>
+      </c>
+      <c r="H48" s="64"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="64"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="62"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="62"/>
+      <c r="G49" s="66">
+        <f>G47-G48</f>
+        <v>1</v>
+      </c>
+      <c r="H49" s="67"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="67"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="23"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" s="28"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+  </mergeCells>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Gestion Stock 2026/BRH 2026/Fiche de Stock Global 2026.xlsx
+++ b/Gestion Stock 2026/BRH 2026/Fiche de Stock Global 2026.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\BRH 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B708AF-B91D-46D2-8537-FDB8F744F3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001F2D92-40D8-4227-920F-5A04B2363A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="13" r:id="rId1"/>
     <sheet name="FEVRIER 2026" sheetId="14" r:id="rId2"/>
     <sheet name="MARS 2026" sheetId="15" r:id="rId3"/>
     <sheet name="AVRIL 2026" sheetId="16" r:id="rId4"/>
+    <sheet name="MAI 2026" sheetId="17" r:id="rId5"/>
+    <sheet name="JUIN 2026" sheetId="18" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="36">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -243,6 +245,54 @@
   <si>
     <t>1 Compteurs DN 30 Destination Agence Beni Slimane</t>
   </si>
+  <si>
+    <r>
+      <t>Mois de MAI</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mois de JUIN</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -251,7 +301,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,6 +387,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -976,7 +1032,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1190,67 +1246,37 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1283,6 +1309,68 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="6" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1838,6 +1926,272 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>473075</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26E94E6A-99A2-4401-9416-D0E4758EE682}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5581650" y="7705725"/>
+          <a:ext cx="958850" cy="1257300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>473075</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C909EF7-3489-4DC7-9ADD-06FD57F0E715}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="10800000">
+          <a:off x="5581650" y="7705725"/>
+          <a:ext cx="958850" cy="1257300"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="T0" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T1" fmla="*/ 0 h 21600"/>
+            <a:gd name="T2" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T3" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T4" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T5" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T6" fmla="*/ 2147483647 w 21600"/>
+            <a:gd name="T7" fmla="*/ 2147483647 h 21600"/>
+            <a:gd name="T8" fmla="*/ 17694720 60000 65536"/>
+            <a:gd name="T9" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T10" fmla="*/ 5898240 60000 65536"/>
+            <a:gd name="T11" fmla="*/ 0 60000 65536"/>
+            <a:gd name="T12" fmla="*/ 12427 w 21600"/>
+            <a:gd name="T13" fmla="*/ 2912 h 21600"/>
+            <a:gd name="T14" fmla="*/ 18227 w 21600"/>
+            <a:gd name="T15" fmla="*/ 9246 h 21600"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="T8">
+              <a:pos x="T0" y="T1"/>
+            </a:cxn>
+            <a:cxn ang="T9">
+              <a:pos x="T2" y="T3"/>
+            </a:cxn>
+            <a:cxn ang="T10">
+              <a:pos x="T4" y="T5"/>
+            </a:cxn>
+            <a:cxn ang="T11">
+              <a:pos x="T6" y="T7"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="T12" t="T13" r="T14" b="T15"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="21600" y="6079"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="15126" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="2912"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="12427" y="2912"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="5564" y="2912"/>
+                <a:pt x="0" y="7052"/>
+                <a:pt x="0" y="12158"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="0" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="6474" y="12158"/>
+              </a:lnTo>
+              <a:cubicBezTo>
+                <a:pt x="6474" y="10550"/>
+                <a:pt x="9139" y="9246"/>
+                <a:pt x="12427" y="9246"/>
+              </a:cubicBezTo>
+              <a:lnTo>
+                <a:pt x="15126" y="9246"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="15126" y="12158"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="21600" y="6079"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -2134,58 +2488,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
-      <c r="G1" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
+      <c r="G1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
       <c r="E2" s="22"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="22"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="83" t="s">
+      <c r="G3" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -2202,61 +2556,61 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="89" t="s">
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="90" t="s">
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="78" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="85"/>
+      <c r="A8" s="73"/>
       <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
@@ -2287,7 +2641,7 @@
       <c r="K8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="91"/>
+      <c r="L8" s="79"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
@@ -3162,149 +3516,149 @@
       <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="74"/>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="75" t="s">
+      <c r="A42" s="80"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="76"/>
-      <c r="I42" s="76" t="s">
+      <c r="H42" s="82"/>
+      <c r="I42" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="77"/>
+      <c r="J42" s="83"/>
       <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
-      <c r="B43" s="61" t="s">
+      <c r="B43" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="62"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="72">
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="86">
         <v>447</v>
       </c>
-      <c r="H43" s="78"/>
-      <c r="I43" s="79"/>
-      <c r="J43" s="80"/>
+      <c r="H43" s="87"/>
+      <c r="I43" s="88"/>
+      <c r="J43" s="89"/>
       <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
-      <c r="B44" s="61" t="s">
+      <c r="B44" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="62"/>
-      <c r="E44" s="62"/>
-      <c r="F44" s="62"/>
-      <c r="G44" s="65">
-        <v>0</v>
-      </c>
-      <c r="H44" s="64"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="64"/>
+      <c r="C44" s="85"/>
+      <c r="D44" s="85"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="85"/>
+      <c r="G44" s="90">
+        <v>0</v>
+      </c>
+      <c r="H44" s="91"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="91"/>
       <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
-      <c r="B45" s="69" t="s">
+      <c r="B45" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="70">
-        <v>0</v>
-      </c>
-      <c r="H45" s="71"/>
-      <c r="I45" s="72"/>
-      <c r="J45" s="73"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="93">
+        <v>0</v>
+      </c>
+      <c r="H45" s="94"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="95"/>
       <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="61" t="s">
+      <c r="B46" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="63">
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="96">
         <f>L40+G45</f>
         <v>116</v>
       </c>
-      <c r="H46" s="64"/>
-      <c r="I46" s="65"/>
-      <c r="J46" s="64"/>
+      <c r="H46" s="91"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="91"/>
       <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
-      <c r="B47" s="61" t="s">
+      <c r="B47" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="62"/>
-      <c r="D47" s="62"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="62"/>
-      <c r="G47" s="63">
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="96">
         <f>G43+G44-G46</f>
         <v>331</v>
       </c>
-      <c r="H47" s="64"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="64"/>
+      <c r="H47" s="91"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="91"/>
       <c r="K47" s="7"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="61" t="s">
+      <c r="B48" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="62"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="63">
+      <c r="C48" s="85"/>
+      <c r="D48" s="85"/>
+      <c r="E48" s="85"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="96">
         <v>321</v>
       </c>
-      <c r="H48" s="64"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="64"/>
+      <c r="H48" s="91"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="91"/>
       <c r="K48" s="7"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
-      <c r="B49" s="61" t="s">
+      <c r="B49" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="62"/>
-      <c r="D49" s="62"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="66">
+      <c r="C49" s="85"/>
+      <c r="D49" s="85"/>
+      <c r="E49" s="85"/>
+      <c r="F49" s="85"/>
+      <c r="G49" s="97">
         <f>G47-G48</f>
         <v>10</v>
       </c>
-      <c r="H49" s="67"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="67"/>
+      <c r="H49" s="98"/>
+      <c r="I49" s="99"/>
+      <c r="J49" s="98"/>
       <c r="K49" s="7"/>
       <c r="L49" s="2"/>
     </row>
@@ -3333,6 +3687,1269 @@
         <v>29</v>
       </c>
     </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+  </mergeCells>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC9BBAA-45FB-4076-A9CF-97F6C48F2A35}">
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+    </row>
+    <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="69" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="72" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="77" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="73"/>
+      <c r="B8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="79"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="46">
+        <v>1</v>
+      </c>
+      <c r="B9" s="43">
+        <v>1</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="54">
+        <v>1</v>
+      </c>
+      <c r="E9" s="34"/>
+      <c r="F9" s="13">
+        <f>SUM(B9:E9)</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="31">
+        <v>21</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="11">
+        <f>SUM(G9:J9)</f>
+        <v>21</v>
+      </c>
+      <c r="L9" s="5">
+        <f>SUM(F9+K9)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>2</v>
+      </c>
+      <c r="B10" s="40">
+        <v>5</v>
+      </c>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="13">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>5</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="11">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="47">
+        <v>3</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="19">
+        <v>11</v>
+      </c>
+      <c r="H11" s="38"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="11">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="47">
+        <v>4</v>
+      </c>
+      <c r="B12" s="40">
+        <v>3</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G12" s="32"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="47">
+        <v>5</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="38">
+        <v>1</v>
+      </c>
+      <c r="H13" s="38"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="47">
+        <v>6</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="47">
+        <v>7</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47">
+        <v>8</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="47">
+        <v>9</v>
+      </c>
+      <c r="B17" s="40">
+        <v>6</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="13">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G17" s="38">
+        <v>1</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47">
+        <v>10</v>
+      </c>
+      <c r="B18" s="40">
+        <v>1</v>
+      </c>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="47">
+        <v>11</v>
+      </c>
+      <c r="B19" s="40">
+        <v>2</v>
+      </c>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="47">
+        <v>12</v>
+      </c>
+      <c r="B20" s="40">
+        <v>2</v>
+      </c>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="47">
+        <v>13</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="47">
+        <v>14</v>
+      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="47">
+        <v>15</v>
+      </c>
+      <c r="B23" s="40">
+        <v>3</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L23" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="47">
+        <v>16</v>
+      </c>
+      <c r="B24" s="40">
+        <v>3</v>
+      </c>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G24" s="19">
+        <v>10</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="11">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L24" s="5">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="47">
+        <v>17</v>
+      </c>
+      <c r="B25" s="40">
+        <v>1</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G25" s="19">
+        <v>10</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14">
+        <v>1</v>
+      </c>
+      <c r="J25" s="14"/>
+      <c r="K25" s="11">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L25" s="5">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="47">
+        <v>18</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <v>10</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="11">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L26" s="5">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="47">
+        <v>19</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="11">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L27" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="47">
+        <v>20</v>
+      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="19"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="47">
+        <v>21</v>
+      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="19"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="47">
+        <v>22</v>
+      </c>
+      <c r="B30" s="40">
+        <v>5</v>
+      </c>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G30" s="19">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L30" s="5">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="47">
+        <v>23</v>
+      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="19"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="47">
+        <v>24</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="19"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="47">
+        <v>25</v>
+      </c>
+      <c r="B33" s="40">
+        <v>1</v>
+      </c>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="19"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="47">
+        <v>26</v>
+      </c>
+      <c r="B34" s="40">
+        <v>2</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="19"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="47">
+        <v>27</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="30"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="47">
+        <v>28</v>
+      </c>
+      <c r="B36" s="44"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="19"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="47">
+        <v>29</v>
+      </c>
+      <c r="B37" s="44"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="19"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="47">
+        <v>30</v>
+      </c>
+      <c r="B38" s="44"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="19"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="49">
+        <v>31</v>
+      </c>
+      <c r="B39" s="45"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="19"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48"/>
+      <c r="B40" s="52">
+        <f>SUM(B9:B39)</f>
+        <v>35</v>
+      </c>
+      <c r="C40" s="52">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="52">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E40" s="52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="51">
+        <f>SUM(F9:F39)</f>
+        <v>36</v>
+      </c>
+      <c r="G40" s="12">
+        <f>SUM(G9:G39)</f>
+        <v>70</v>
+      </c>
+      <c r="H40" s="12">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="12">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="12">
+        <f t="shared" si="4"/>
+        <v>71</v>
+      </c>
+      <c r="L40" s="12">
+        <f t="shared" si="4"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="9"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="80"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="82"/>
+      <c r="I42" s="82" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="9"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="86">
+        <v>321</v>
+      </c>
+      <c r="H43" s="87"/>
+      <c r="I43" s="88"/>
+      <c r="J43" s="89"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="9"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="84" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="85"/>
+      <c r="D44" s="85"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="85"/>
+      <c r="G44" s="90">
+        <v>0</v>
+      </c>
+      <c r="H44" s="91"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="91"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="9"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="93">
+        <v>0</v>
+      </c>
+      <c r="H45" s="94"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="95"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="9"/>
+    </row>
+    <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="96">
+        <f>L40+G45</f>
+        <v>107</v>
+      </c>
+      <c r="H46" s="91"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="91"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="9"/>
+    </row>
+    <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="84" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="96">
+        <f>G43+G44-G46</f>
+        <v>214</v>
+      </c>
+      <c r="H47" s="91"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="91"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="85"/>
+      <c r="D48" s="85"/>
+      <c r="E48" s="85"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="96">
+        <v>214</v>
+      </c>
+      <c r="H48" s="91"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="91"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="85"/>
+      <c r="D49" s="85"/>
+      <c r="E49" s="85"/>
+      <c r="F49" s="85"/>
+      <c r="G49" s="97">
+        <f>G47-G48</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="98"/>
+      <c r="I49" s="99"/>
+      <c r="J49" s="98"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="23"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" s="28"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
     <mergeCell ref="B48:F48"/>
@@ -3378,8 +4995,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC9BBAA-45FB-4076-A9CF-97F6C48F2A35}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F79BFF48-00BC-419E-8391-D515B4A2FE9A}">
   <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3388,58 +5005,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
-      <c r="G1" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
+      <c r="G1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
       <c r="E2" s="22"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="22"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="83" t="s">
+      <c r="G3" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -3456,61 +5073,61 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="82" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
+      <c r="A6" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="89" t="s">
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="90" t="s">
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="78" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="85"/>
+      <c r="A8" s="73"/>
       <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
@@ -3541,7 +5158,7 @@
       <c r="K8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="91"/>
+      <c r="L8" s="79"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
@@ -3550,28 +5167,28 @@
       <c r="B9" s="43">
         <v>1</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="54">
-        <v>1</v>
-      </c>
-      <c r="E9" s="34"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="56"/>
       <c r="F9" s="13">
         <f>SUM(B9:E9)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="31">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H9" s="35"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
+      <c r="I9" s="55">
+        <v>1</v>
+      </c>
+      <c r="J9" s="55"/>
       <c r="K9" s="11">
         <f>SUM(G9:J9)</f>
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L9" s="5">
         <f>SUM(F9+K9)</f>
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3579,53 +5196,55 @@
         <v>2</v>
       </c>
       <c r="B10" s="40">
-        <v>5</v>
-      </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="37"/>
+        <v>1</v>
+      </c>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="39"/>
       <c r="F10" s="13">
         <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
-        <v>5</v>
-      </c>
-      <c r="G10" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="19">
+        <v>1</v>
+      </c>
       <c r="H10" s="38"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
       <c r="K10" s="11">
         <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>3</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
+      <c r="B11" s="40">
+        <v>5</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="39"/>
       <c r="F11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="19">
-        <v>11</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G11" s="19"/>
       <c r="H11" s="38"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
       <c r="K11" s="11">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3633,22 +5252,24 @@
         <v>4</v>
       </c>
       <c r="B12" s="40">
-        <v>3</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="37"/>
+        <v>1</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="39"/>
       <c r="F12" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G12" s="32"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="32">
+        <v>2</v>
+      </c>
       <c r="H12" s="38"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
       <c r="K12" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="2"/>
@@ -3660,26 +5281,26 @@
         <v>5</v>
       </c>
       <c r="B13" s="40"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="39"/>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G13" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="38"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
       <c r="K13" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3687,17 +5308,17 @@
         <v>6</v>
       </c>
       <c r="B14" s="40"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="37"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="39"/>
       <c r="F14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G14" s="38"/>
       <c r="H14" s="38"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
       <c r="K14" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3712,8 +5333,8 @@
         <v>7</v>
       </c>
       <c r="B15" s="40"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="39"/>
       <c r="F15" s="13">
         <f t="shared" si="0"/>
@@ -3721,8 +5342,8 @@
       </c>
       <c r="G15" s="38"/>
       <c r="H15" s="38"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3737,17 +5358,17 @@
         <v>8</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="37"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="39"/>
       <c r="F16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="38"/>
       <c r="H16" s="38"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
       <c r="K16" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3761,29 +5382,25 @@
       <c r="A17" s="47">
         <v>9</v>
       </c>
-      <c r="B17" s="40">
-        <v>6</v>
-      </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="37"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="39"/>
       <c r="F17" s="13">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="G17" s="38">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G17" s="38"/>
       <c r="H17" s="38"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
       <c r="K17" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3791,80 +5408,76 @@
         <v>10</v>
       </c>
       <c r="B18" s="40">
-        <v>1</v>
-      </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="37"/>
+        <v>10</v>
+      </c>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="39"/>
       <c r="F18" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G18" s="40"/>
       <c r="H18" s="40"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
       <c r="K18" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="47">
         <v>11</v>
       </c>
-      <c r="B19" s="40">
-        <v>2</v>
-      </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="37"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="39"/>
       <c r="F19" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="38"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
       <c r="K19" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>12</v>
       </c>
-      <c r="B20" s="40">
-        <v>2</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="37"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="39"/>
       <c r="F20" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="19"/>
       <c r="H20" s="38"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
       <c r="K20" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3872,17 +5485,17 @@
         <v>13</v>
       </c>
       <c r="B21" s="40"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="37"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="39"/>
       <c r="F21" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="41"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
       <c r="K21" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3897,17 +5510,17 @@
         <v>14</v>
       </c>
       <c r="B22" s="40"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="39"/>
       <c r="F22" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G22" s="21"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
       <c r="K22" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3921,29 +5534,27 @@
       <c r="A23" s="47">
         <v>15</v>
       </c>
-      <c r="B23" s="40">
-        <v>3</v>
-      </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="39"/>
       <c r="F23" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G23" s="19">
         <v>1</v>
       </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
       <c r="K23" s="11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3953,57 +5564,51 @@
       <c r="B24" s="40">
         <v>3</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="37"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="39"/>
       <c r="F24" s="13">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G24" s="19">
-        <v>10</v>
-      </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
       <c r="K24" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="47">
         <v>17</v>
       </c>
-      <c r="B25" s="40">
-        <v>1</v>
-      </c>
+      <c r="B25" s="40"/>
       <c r="C25" s="40"/>
       <c r="D25" s="42"/>
-      <c r="E25" s="37"/>
+      <c r="E25" s="39"/>
       <c r="F25" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G25" s="19">
-        <v>10</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14">
-        <v>1</v>
-      </c>
-      <c r="J25" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="19"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
       <c r="K25" s="11">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4011,53 +5616,51 @@
         <v>18</v>
       </c>
       <c r="B26" s="40"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="37"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="39"/>
       <c r="F26" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G26" s="19">
-        <v>10</v>
-      </c>
+      <c r="G26" s="19"/>
       <c r="H26" s="53"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
       <c r="K26" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="47">
         <v>19</v>
       </c>
-      <c r="B27" s="40"/>
+      <c r="B27" s="40">
+        <v>1</v>
+      </c>
       <c r="C27" s="42"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="39"/>
       <c r="F27" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="19">
-        <v>4</v>
-      </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="G27" s="19"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
       <c r="K27" s="11">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4065,17 +5668,17 @@
         <v>20</v>
       </c>
       <c r="B28" s="40"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="37"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="39"/>
       <c r="F28" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G28" s="19"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
       <c r="K28" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4090,17 +5693,17 @@
         <v>21</v>
       </c>
       <c r="B29" s="40"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="37"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="39"/>
       <c r="F29" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G29" s="19"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
       <c r="K29" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4114,54 +5717,52 @@
       <c r="A30" s="47">
         <v>22</v>
       </c>
-      <c r="B30" s="40">
-        <v>5</v>
-      </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="39"/>
       <c r="F30" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G30" s="19">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="19"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
       <c r="K30" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="47">
         <v>23</v>
       </c>
-      <c r="B31" s="40"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37"/>
+      <c r="B31" s="40">
+        <v>3</v>
+      </c>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="39"/>
       <c r="F31" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="19"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
       <c r="K31" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4169,17 +5770,17 @@
         <v>24</v>
       </c>
       <c r="B32" s="40"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="37"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="39"/>
       <c r="F32" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G32" s="19"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
       <c r="K32" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4194,26 +5795,26 @@
         <v>25</v>
       </c>
       <c r="B33" s="40">
-        <v>1</v>
-      </c>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="37"/>
+        <v>2</v>
+      </c>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="39"/>
       <c r="F33" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="19"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
       <c r="K33" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4221,26 +5822,30 @@
         <v>26</v>
       </c>
       <c r="B34" s="40">
+        <v>1</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42">
         <v>2</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="37"/>
+      <c r="E34" s="39"/>
       <c r="F34" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G34" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="G34" s="19">
+        <v>1</v>
+      </c>
       <c r="H34" s="38"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
       <c r="K34" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4248,17 +5853,17 @@
         <v>27</v>
       </c>
       <c r="B35" s="44"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="37"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="39"/>
       <c r="F35" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G35" s="30"/>
       <c r="H35" s="38"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
       <c r="K35" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4273,17 +5878,17 @@
         <v>28</v>
       </c>
       <c r="B36" s="44"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="15"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="58"/>
       <c r="F36" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G36" s="19"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
       <c r="K36" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4298,24 +5903,26 @@
         <v>29</v>
       </c>
       <c r="B37" s="44"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="15"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53">
+        <v>1</v>
+      </c>
+      <c r="E37" s="58"/>
       <c r="F37" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="19"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
       <c r="K37" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4323,17 +5930,17 @@
         <v>30</v>
       </c>
       <c r="B38" s="44"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="15"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="58"/>
       <c r="F38" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G38" s="19"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
       <c r="K38" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4347,32 +5954,36 @@
       <c r="A39" s="49">
         <v>31</v>
       </c>
-      <c r="B39" s="45"/>
-      <c r="C39" s="16"/>
+      <c r="B39" s="45">
+        <v>3</v>
+      </c>
+      <c r="C39" s="59"/>
       <c r="D39" s="45"/>
-      <c r="E39" s="17"/>
+      <c r="E39" s="60"/>
       <c r="F39" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="19"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
+        <v>3</v>
+      </c>
+      <c r="G39" s="19">
+        <v>1</v>
+      </c>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
       <c r="K39" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="48"/>
       <c r="B40" s="52">
         <f>SUM(B9:B39)</f>
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C40" s="52">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -4380,7 +5991,7 @@
       </c>
       <c r="D40" s="52">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="52">
         <f t="shared" si="3"/>
@@ -4388,11 +5999,11 @@
       </c>
       <c r="F40" s="51">
         <f>SUM(F9:F39)</f>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G40" s="12">
         <f>SUM(G9:G39)</f>
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
@@ -4408,11 +6019,11 @@
       </c>
       <c r="K40" s="12">
         <f t="shared" si="4"/>
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="4"/>
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4430,149 +6041,149 @@
       <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="74"/>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="75" t="s">
+      <c r="A42" s="80"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="76"/>
-      <c r="I42" s="76" t="s">
+      <c r="H42" s="82"/>
+      <c r="I42" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="77"/>
+      <c r="J42" s="83"/>
       <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
-      <c r="B43" s="61" t="s">
+      <c r="B43" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="62"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="72">
-        <v>321</v>
-      </c>
-      <c r="H43" s="78"/>
-      <c r="I43" s="79"/>
-      <c r="J43" s="80"/>
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="86">
+        <v>214</v>
+      </c>
+      <c r="H43" s="87"/>
+      <c r="I43" s="88"/>
+      <c r="J43" s="89"/>
       <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
-      <c r="B44" s="61" t="s">
+      <c r="B44" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="62"/>
-      <c r="E44" s="62"/>
-      <c r="F44" s="62"/>
-      <c r="G44" s="65">
-        <v>0</v>
-      </c>
-      <c r="H44" s="64"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="64"/>
+      <c r="C44" s="85"/>
+      <c r="D44" s="85"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="85"/>
+      <c r="G44" s="90">
+        <v>0</v>
+      </c>
+      <c r="H44" s="91"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="91"/>
       <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
-      <c r="B45" s="69" t="s">
+      <c r="B45" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="70">
-        <v>0</v>
-      </c>
-      <c r="H45" s="71"/>
-      <c r="I45" s="72"/>
-      <c r="J45" s="73"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="93">
+        <v>0</v>
+      </c>
+      <c r="H45" s="94"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="95"/>
       <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="61" t="s">
+      <c r="B46" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="63">
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="96">
         <f>L40+G45</f>
-        <v>107</v>
-      </c>
-      <c r="H46" s="64"/>
-      <c r="I46" s="65"/>
-      <c r="J46" s="64"/>
+        <v>45</v>
+      </c>
+      <c r="H46" s="91"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="91"/>
       <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
-      <c r="B47" s="61" t="s">
+      <c r="B47" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="62"/>
-      <c r="D47" s="62"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="62"/>
-      <c r="G47" s="63">
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="96">
         <f>G43+G44-G46</f>
-        <v>214</v>
-      </c>
-      <c r="H47" s="64"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="64"/>
+        <v>169</v>
+      </c>
+      <c r="H47" s="91"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="91"/>
       <c r="K47" s="7"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="61" t="s">
+      <c r="B48" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="62"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="63">
-        <v>214</v>
-      </c>
-      <c r="H48" s="64"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="64"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="85"/>
+      <c r="E48" s="85"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="96">
+        <v>169</v>
+      </c>
+      <c r="H48" s="91"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="91"/>
       <c r="K48" s="7"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
-      <c r="B49" s="61" t="s">
+      <c r="B49" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="62"/>
-      <c r="D49" s="62"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="66">
+      <c r="C49" s="85"/>
+      <c r="D49" s="85"/>
+      <c r="E49" s="85"/>
+      <c r="F49" s="85"/>
+      <c r="G49" s="97">
         <f>G47-G48</f>
         <v>0</v>
       </c>
-      <c r="H49" s="67"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="67"/>
+      <c r="H49" s="98"/>
+      <c r="I49" s="99"/>
+      <c r="J49" s="98"/>
       <c r="K49" s="7"/>
       <c r="L49" s="2"/>
     </row>
@@ -4641,9 +6252,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F79BFF48-00BC-419E-8391-D515B4A2FE9A}">
-  <dimension ref="A1:L52"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6601AF8D-E42B-49F4-9FB8-5130A136BA40}">
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -4651,58 +6262,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
-      <c r="G1" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
+      <c r="G1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
       <c r="E2" s="22"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="22"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="83" t="s">
+      <c r="G3" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -4719,61 +6330,61 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="82" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
+      <c r="A6" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="89" t="s">
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="90" t="s">
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="78" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="85"/>
+      <c r="A8" s="73"/>
       <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
@@ -4804,33 +6415,29 @@
       <c r="K8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="91"/>
+      <c r="L8" s="79"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
         <v>1</v>
       </c>
       <c r="B9" s="43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" s="54"/>
       <c r="D9" s="54"/>
       <c r="E9" s="56"/>
       <c r="F9" s="13">
         <f>SUM(B9:E9)</f>
-        <v>1</v>
-      </c>
-      <c r="G9" s="31">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G9" s="31"/>
       <c r="H9" s="35"/>
-      <c r="I9" s="55">
-        <v>1</v>
-      </c>
+      <c r="I9" s="55"/>
       <c r="J9" s="55"/>
       <c r="K9" s="11">
         <f>SUM(G9:J9)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
         <f>SUM(F9+K9)</f>
@@ -4841,44 +6448,38 @@
       <c r="A10" s="6">
         <v>2</v>
       </c>
-      <c r="B10" s="40">
-        <v>1</v>
-      </c>
+      <c r="B10" s="40"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
       <c r="E10" s="39"/>
       <c r="F10" s="13">
         <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
-        <v>1</v>
-      </c>
-      <c r="G10" s="19">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" s="19"/>
       <c r="H10" s="38"/>
       <c r="I10" s="53"/>
       <c r="J10" s="53"/>
       <c r="K10" s="11">
         <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>3</v>
       </c>
-      <c r="B11" s="40">
-        <v>5</v>
-      </c>
+      <c r="B11" s="40"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
       <c r="E11" s="39"/>
       <c r="F11" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="38"/>
@@ -4890,63 +6491,63 @@
       </c>
       <c r="L11" s="5">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47">
         <v>4</v>
       </c>
-      <c r="B12" s="40">
-        <v>1</v>
-      </c>
+      <c r="B12" s="40"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
       <c r="E12" s="39"/>
       <c r="F12" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G12" s="32">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G12" s="32"/>
       <c r="H12" s="38"/>
       <c r="I12" s="53"/>
       <c r="J12" s="53"/>
       <c r="K12" s="11">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47">
         <v>5</v>
       </c>
-      <c r="B13" s="40"/>
+      <c r="B13" s="40">
+        <v>2</v>
+      </c>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
       <c r="E13" s="39"/>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" s="38"/>
-      <c r="I13" s="53"/>
+      <c r="I13" s="53">
+        <v>1</v>
+      </c>
       <c r="J13" s="53"/>
       <c r="K13" s="11">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4978,25 +6579,29 @@
       <c r="A15" s="47">
         <v>7</v>
       </c>
-      <c r="B15" s="40"/>
+      <c r="B15" s="40">
+        <v>5</v>
+      </c>
       <c r="C15" s="42"/>
       <c r="D15" s="42"/>
       <c r="E15" s="39"/>
       <c r="F15" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="38"/>
+        <v>5</v>
+      </c>
+      <c r="G15" s="38">
+        <v>7</v>
+      </c>
       <c r="H15" s="38"/>
       <c r="I15" s="53"/>
       <c r="J15" s="53"/>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5011,17 +6616,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
+      <c r="G16" s="38">
+        <v>12</v>
+      </c>
+      <c r="H16" s="38">
+        <v>1</v>
+      </c>
       <c r="I16" s="53"/>
       <c r="J16" s="53"/>
       <c r="K16" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5053,15 +6662,13 @@
       <c r="A18" s="47">
         <v>10</v>
       </c>
-      <c r="B18" s="40">
-        <v>10</v>
-      </c>
+      <c r="B18" s="40"/>
       <c r="C18" s="42"/>
       <c r="D18" s="42"/>
       <c r="E18" s="39"/>
       <c r="F18" s="13">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G18" s="40"/>
       <c r="H18" s="40"/>
@@ -5073,7 +6680,7 @@
       </c>
       <c r="L18" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5105,13 +6712,17 @@
       <c r="A20" s="47">
         <v>12</v>
       </c>
-      <c r="B20" s="40"/>
+      <c r="B20" s="40">
+        <v>2</v>
+      </c>
       <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
+      <c r="D20" s="42">
+        <v>2</v>
+      </c>
       <c r="E20" s="39"/>
       <c r="F20" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" s="19"/>
       <c r="H20" s="38"/>
@@ -5123,7 +6734,7 @@
       </c>
       <c r="L20" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5138,30 +6749,34 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="21"/>
+      <c r="G21" s="21">
+        <v>2</v>
+      </c>
       <c r="H21" s="41"/>
       <c r="I21" s="53"/>
       <c r="J21" s="53"/>
       <c r="K21" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="47">
         <v>14</v>
       </c>
-      <c r="B22" s="40"/>
+      <c r="B22" s="40">
+        <v>1</v>
+      </c>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
       <c r="E22" s="39"/>
       <c r="F22" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="53"/>
@@ -5173,34 +6788,38 @@
       </c>
       <c r="L22" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="47">
         <v>15</v>
       </c>
-      <c r="B23" s="40"/>
+      <c r="B23" s="40">
+        <v>2</v>
+      </c>
       <c r="C23" s="42"/>
       <c r="D23" s="42"/>
       <c r="E23" s="39"/>
       <c r="F23" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="19">
         <v>1</v>
       </c>
-      <c r="H23" s="53"/>
+      <c r="H23" s="53">
+        <v>1</v>
+      </c>
       <c r="I23" s="53"/>
       <c r="J23" s="53"/>
       <c r="K23" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5208,28 +6827,26 @@
         <v>16</v>
       </c>
       <c r="B24" s="40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="42"/>
       <c r="D24" s="42"/>
       <c r="E24" s="39"/>
       <c r="F24" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G24" s="19">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G24" s="19"/>
       <c r="H24" s="53"/>
       <c r="I24" s="53"/>
       <c r="J24" s="53"/>
       <c r="K24" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5261,40 +6878,42 @@
       <c r="A26" s="47">
         <v>18</v>
       </c>
-      <c r="B26" s="40"/>
+      <c r="B26" s="40">
+        <v>2</v>
+      </c>
       <c r="C26" s="42"/>
       <c r="D26" s="42"/>
       <c r="E26" s="39"/>
       <c r="F26" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
+      <c r="I26" s="53">
+        <v>1</v>
+      </c>
       <c r="J26" s="53"/>
       <c r="K26" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="47">
         <v>19</v>
       </c>
-      <c r="B27" s="40">
-        <v>1</v>
-      </c>
+      <c r="B27" s="40"/>
       <c r="C27" s="42"/>
       <c r="D27" s="42"/>
       <c r="E27" s="39"/>
       <c r="F27" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="19"/>
       <c r="H27" s="53"/>
@@ -5306,7 +6925,7 @@
       </c>
       <c r="L27" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5338,38 +6957,44 @@
       <c r="A29" s="47">
         <v>21</v>
       </c>
-      <c r="B29" s="40"/>
+      <c r="B29" s="40">
+        <v>1</v>
+      </c>
       <c r="C29" s="42"/>
       <c r="D29" s="42"/>
       <c r="E29" s="39"/>
       <c r="F29" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="G29" s="19">
+        <v>9</v>
+      </c>
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
       <c r="J29" s="53"/>
       <c r="K29" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="47">
         <v>22</v>
       </c>
-      <c r="B30" s="40"/>
+      <c r="B30" s="40">
+        <v>6</v>
+      </c>
       <c r="C30" s="42"/>
       <c r="D30" s="42"/>
       <c r="E30" s="39"/>
       <c r="F30" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G30" s="19"/>
       <c r="H30" s="53"/>
@@ -5381,7 +7006,7 @@
       </c>
       <c r="L30" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5389,14 +7014,14 @@
         <v>23</v>
       </c>
       <c r="B31" s="40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="42"/>
       <c r="D31" s="42"/>
       <c r="E31" s="39"/>
       <c r="F31" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="19"/>
       <c r="H31" s="53"/>
@@ -5408,7 +7033,7 @@
       </c>
       <c r="L31" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5440,27 +7065,27 @@
       <c r="A33" s="47">
         <v>25</v>
       </c>
-      <c r="B33" s="40">
-        <v>2</v>
-      </c>
+      <c r="B33" s="40"/>
       <c r="C33" s="42"/>
       <c r="D33" s="42"/>
       <c r="E33" s="39"/>
       <c r="F33" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G33" s="19"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="19">
+        <v>10</v>
+      </c>
       <c r="H33" s="53"/>
       <c r="I33" s="53"/>
       <c r="J33" s="53"/>
       <c r="K33" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5468,26 +7093,22 @@
         <v>26</v>
       </c>
       <c r="B34" s="40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34" s="42"/>
-      <c r="D34" s="42">
-        <v>2</v>
-      </c>
+      <c r="D34" s="42"/>
       <c r="E34" s="39"/>
       <c r="F34" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G34" s="19">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G34" s="19"/>
       <c r="H34" s="38"/>
       <c r="I34" s="53"/>
       <c r="J34" s="53"/>
       <c r="K34" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="2"/>
@@ -5498,38 +7119,44 @@
       <c r="A35" s="47">
         <v>27</v>
       </c>
-      <c r="B35" s="44"/>
+      <c r="B35" s="44">
+        <v>1</v>
+      </c>
       <c r="C35" s="42"/>
       <c r="D35" s="42"/>
       <c r="E35" s="39"/>
       <c r="F35" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="30"/>
-      <c r="H35" s="38"/>
+      <c r="H35" s="38">
+        <v>1</v>
+      </c>
       <c r="I35" s="53"/>
       <c r="J35" s="53"/>
       <c r="K35" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="47">
         <v>28</v>
       </c>
-      <c r="B36" s="44"/>
+      <c r="B36" s="44">
+        <v>3</v>
+      </c>
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
       <c r="E36" s="58"/>
       <c r="F36" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" s="19"/>
       <c r="H36" s="53"/>
@@ -5541,7 +7168,7 @@
       </c>
       <c r="L36" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5550,38 +7177,40 @@
       </c>
       <c r="B37" s="44"/>
       <c r="C37" s="53"/>
-      <c r="D37" s="53">
-        <v>1</v>
-      </c>
+      <c r="D37" s="53"/>
       <c r="E37" s="58"/>
       <c r="F37" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G37" s="19"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="19">
+        <v>3</v>
+      </c>
       <c r="H37" s="53"/>
       <c r="I37" s="53"/>
       <c r="J37" s="53"/>
       <c r="K37" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="47">
         <v>30</v>
       </c>
-      <c r="B38" s="44"/>
+      <c r="B38" s="44">
+        <v>2</v>
+      </c>
       <c r="C38" s="53"/>
       <c r="D38" s="53"/>
       <c r="E38" s="58"/>
       <c r="F38" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="19"/>
       <c r="H38" s="53"/>
@@ -5593,43 +7222,39 @@
       </c>
       <c r="L38" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="49">
         <v>31</v>
       </c>
-      <c r="B39" s="45">
-        <v>3</v>
-      </c>
+      <c r="B39" s="45"/>
       <c r="C39" s="59"/>
       <c r="D39" s="45"/>
       <c r="E39" s="60"/>
       <c r="F39" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G39" s="19">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G39" s="19"/>
       <c r="H39" s="53"/>
       <c r="I39" s="53"/>
       <c r="J39" s="53"/>
       <c r="K39" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="48"/>
       <c r="B40" s="52">
         <f>SUM(B9:B39)</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C40" s="52">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -5637,7 +7262,7 @@
       </c>
       <c r="D40" s="52">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="52">
         <f t="shared" si="3"/>
@@ -5645,19 +7270,19 @@
       </c>
       <c r="F40" s="51">
         <f>SUM(F9:F39)</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G40" s="12">
         <f>SUM(G9:G39)</f>
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" s="12">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" s="12">
         <f t="shared" si="4"/>
@@ -5665,11 +7290,11 @@
       </c>
       <c r="K40" s="12">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="4"/>
-        <v>45</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5687,149 +7312,1409 @@
       <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="74"/>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="75" t="s">
+      <c r="A42" s="80"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="76"/>
-      <c r="I42" s="76" t="s">
+      <c r="H42" s="82"/>
+      <c r="I42" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="77"/>
+      <c r="J42" s="83"/>
       <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
-      <c r="B43" s="61" t="s">
+      <c r="B43" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="62"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="72">
-        <v>214</v>
-      </c>
-      <c r="H43" s="78"/>
-      <c r="I43" s="79"/>
-      <c r="J43" s="80"/>
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="86">
+        <v>169</v>
+      </c>
+      <c r="H43" s="87"/>
+      <c r="I43" s="88"/>
+      <c r="J43" s="89"/>
       <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
-      <c r="B44" s="61" t="s">
+      <c r="B44" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="62"/>
-      <c r="E44" s="62"/>
-      <c r="F44" s="62"/>
-      <c r="G44" s="65">
-        <v>0</v>
-      </c>
-      <c r="H44" s="64"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="64"/>
+      <c r="C44" s="85"/>
+      <c r="D44" s="85"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="85"/>
+      <c r="G44" s="90">
+        <v>1</v>
+      </c>
+      <c r="H44" s="91"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="91"/>
       <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
-      <c r="B45" s="69" t="s">
+      <c r="B45" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="70">
-        <v>0</v>
-      </c>
-      <c r="H45" s="71"/>
-      <c r="I45" s="72"/>
-      <c r="J45" s="73"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="93">
+        <v>0</v>
+      </c>
+      <c r="H45" s="94"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="95"/>
       <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="61" t="s">
+      <c r="B46" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="63">
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="96">
         <f>L40+G45</f>
-        <v>45</v>
-      </c>
-      <c r="H46" s="64"/>
-      <c r="I46" s="65"/>
-      <c r="J46" s="64"/>
+        <v>91</v>
+      </c>
+      <c r="H46" s="91"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="91"/>
       <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
-      <c r="B47" s="61" t="s">
+      <c r="B47" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="62"/>
-      <c r="D47" s="62"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="62"/>
-      <c r="G47" s="63">
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="96">
         <f>G43+G44-G46</f>
-        <v>169</v>
-      </c>
-      <c r="H47" s="64"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="64"/>
+        <v>79</v>
+      </c>
+      <c r="H47" s="91"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="91"/>
       <c r="K47" s="7"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="61" t="s">
+      <c r="B48" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="62"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="63">
-        <v>169</v>
-      </c>
-      <c r="H48" s="64"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="64"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="85"/>
+      <c r="E48" s="85"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="96">
+        <v>78</v>
+      </c>
+      <c r="H48" s="91"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="91"/>
       <c r="K48" s="7"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
-      <c r="B49" s="61" t="s">
+      <c r="B49" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="62"/>
-      <c r="D49" s="62"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="66">
+      <c r="C49" s="85"/>
+      <c r="D49" s="85"/>
+      <c r="E49" s="85"/>
+      <c r="F49" s="85"/>
+      <c r="G49" s="97">
         <f>G47-G48</f>
-        <v>0</v>
-      </c>
-      <c r="H49" s="67"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="67"/>
+        <v>1</v>
+      </c>
+      <c r="H49" s="98"/>
+      <c r="I49" s="99"/>
+      <c r="J49" s="98"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="23"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" s="28"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:L3"/>
+  </mergeCells>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FAF46B-8750-447C-882C-CF6DE900AB4A}">
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="12" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+    </row>
+    <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="69" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="72" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="77" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="73"/>
+      <c r="B8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="79"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="46">
+        <v>1</v>
+      </c>
+      <c r="B9" s="61"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="13">
+        <f>SUM(B9:E9)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="35"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="11">
+        <f>SUM(G9:J9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <f>SUM(F9+K9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>2</v>
+      </c>
+      <c r="B10" s="62">
+        <v>1</v>
+      </c>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="13">
+        <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
+        <v>1</v>
+      </c>
+      <c r="G10" s="38"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="11">
+        <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" ref="L10:L39" si="2">SUM(F10+K10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="47">
+        <v>3</v>
+      </c>
+      <c r="B11" s="62"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="39">
+        <v>1</v>
+      </c>
+      <c r="F11" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="38">
+        <v>1</v>
+      </c>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42">
+        <v>1</v>
+      </c>
+      <c r="K11" s="11">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="47">
+        <v>4</v>
+      </c>
+      <c r="B12" s="62"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="38">
+        <v>1</v>
+      </c>
+      <c r="H12" s="42">
+        <v>1</v>
+      </c>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42">
+        <v>1</v>
+      </c>
+      <c r="K12" s="11">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="47">
+        <v>5</v>
+      </c>
+      <c r="B13" s="62"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="38"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="47">
+        <v>6</v>
+      </c>
+      <c r="B14" s="62">
+        <v>15</v>
+      </c>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="47">
+        <v>7</v>
+      </c>
+      <c r="B15" s="62"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="38"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47">
+        <v>8</v>
+      </c>
+      <c r="B16" s="62"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="38"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="47">
+        <v>9</v>
+      </c>
+      <c r="B17" s="62"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="38">
+        <v>1</v>
+      </c>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="47">
+        <v>10</v>
+      </c>
+      <c r="B18" s="62">
+        <v>8</v>
+      </c>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="13">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G18" s="38"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="47">
+        <v>11</v>
+      </c>
+      <c r="B19" s="62">
+        <v>1</v>
+      </c>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G19" s="38"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="47">
+        <v>12</v>
+      </c>
+      <c r="B20" s="62"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="47">
+        <v>13</v>
+      </c>
+      <c r="B21" s="62">
+        <v>6</v>
+      </c>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42">
+        <v>2</v>
+      </c>
+      <c r="E21" s="39"/>
+      <c r="F21" s="13">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G21" s="38"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="47">
+        <v>14</v>
+      </c>
+      <c r="B22" s="62"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="38"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="47">
+        <v>15</v>
+      </c>
+      <c r="B23" s="62"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="47">
+        <v>16</v>
+      </c>
+      <c r="B24" s="62"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="38"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="47">
+        <v>17</v>
+      </c>
+      <c r="B25" s="62"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="38"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="47">
+        <v>18</v>
+      </c>
+      <c r="B26" s="62"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="47">
+        <v>19</v>
+      </c>
+      <c r="B27" s="62"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="38"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="47">
+        <v>20</v>
+      </c>
+      <c r="B28" s="62"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="38"/>
+      <c r="H28" s="42">
+        <v>3</v>
+      </c>
+      <c r="I28" s="42"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="11">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L28" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="47">
+        <v>21</v>
+      </c>
+      <c r="B29" s="62"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="38"/>
+      <c r="H29" s="42">
+        <v>1</v>
+      </c>
+      <c r="I29" s="42">
+        <v>1</v>
+      </c>
+      <c r="J29" s="38">
+        <v>2</v>
+      </c>
+      <c r="K29" s="11">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L29" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="47">
+        <v>22</v>
+      </c>
+      <c r="B30" s="62"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="38"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="47">
+        <v>23</v>
+      </c>
+      <c r="B31" s="62"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="38"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="47">
+        <v>24</v>
+      </c>
+      <c r="B32" s="62"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="38"/>
+      <c r="H32" s="42">
+        <v>1</v>
+      </c>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L32" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="47">
+        <v>25</v>
+      </c>
+      <c r="B33" s="62"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="38"/>
+      <c r="H33" s="42">
+        <v>2</v>
+      </c>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="11">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L33" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="47">
+        <v>26</v>
+      </c>
+      <c r="B34" s="62">
+        <v>1</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G34" s="38"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="47">
+        <v>27</v>
+      </c>
+      <c r="B35" s="62"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="68"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="47">
+        <v>28</v>
+      </c>
+      <c r="B36" s="62"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="38"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="47">
+        <v>29</v>
+      </c>
+      <c r="B37" s="62"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="38"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="47">
+        <v>30</v>
+      </c>
+      <c r="B38" s="62"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="38"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="49">
+        <v>31</v>
+      </c>
+      <c r="B39" s="64"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="38"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42">
+        <v>1</v>
+      </c>
+      <c r="K39" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L39" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="48"/>
+      <c r="B40" s="52">
+        <f>SUM(B9:B39)</f>
+        <v>32</v>
+      </c>
+      <c r="C40" s="52">
+        <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="52">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="E40" s="52">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F40" s="51">
+        <f>SUM(F9:F39)</f>
+        <v>35</v>
+      </c>
+      <c r="G40" s="12">
+        <f>SUM(G9:G39)</f>
+        <v>3</v>
+      </c>
+      <c r="H40" s="12">
+        <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
+        <v>8</v>
+      </c>
+      <c r="I40" s="12">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="12">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K40" s="12">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="L40" s="12">
+        <f t="shared" si="4"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="9"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="80"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="82"/>
+      <c r="I42" s="82" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="83"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="9"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="86">
+        <v>78</v>
+      </c>
+      <c r="H43" s="87"/>
+      <c r="I43" s="88"/>
+      <c r="J43" s="89"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="9"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="84" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="85"/>
+      <c r="D44" s="85"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="85"/>
+      <c r="G44" s="90">
+        <v>35</v>
+      </c>
+      <c r="H44" s="91"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="91"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="9"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="93">
+        <v>0</v>
+      </c>
+      <c r="H45" s="94"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="95"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="9"/>
+    </row>
+    <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="96">
+        <f>L40+G45</f>
+        <v>52</v>
+      </c>
+      <c r="H46" s="91"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="91"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="9"/>
+    </row>
+    <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="84" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="96">
+        <f>G43+G44-G46</f>
+        <v>61</v>
+      </c>
+      <c r="H47" s="91"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="91"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="85"/>
+      <c r="D48" s="85"/>
+      <c r="E48" s="85"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="96">
+        <v>61</v>
+      </c>
+      <c r="H48" s="91"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="91"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="85"/>
+      <c r="D49" s="85"/>
+      <c r="E49" s="85"/>
+      <c r="F49" s="85"/>
+      <c r="G49" s="97">
+        <f>G47-G48</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="98"/>
+      <c r="I49" s="99"/>
+      <c r="J49" s="98"/>
       <c r="K49" s="7"/>
       <c r="L49" s="2"/>
     </row>
@@ -5898,9 +8783,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6601AF8D-E42B-49F4-9FB8-5130A136BA40}">
-  <dimension ref="A1:L53"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51380AB1-D806-4C75-83FD-25C579CF281A}">
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -5908,58 +8793,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
       <c r="E1" s="22"/>
       <c r="F1" s="23"/>
-      <c r="G1" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
+      <c r="G1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
       <c r="E2" s="22"/>
       <c r="F2" s="23"/>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="22"/>
       <c r="F3" s="23"/>
-      <c r="G3" s="83" t="s">
+      <c r="G3" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -5976,61 +8861,61 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="82" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
+      <c r="A6" s="70" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="89" t="s">
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="90" t="s">
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="78" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="85"/>
+      <c r="A8" s="73"/>
       <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
@@ -6061,40 +8946,38 @@
       <c r="K8" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="91"/>
+      <c r="L8" s="79"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
         <v>1</v>
       </c>
-      <c r="B9" s="43">
-        <v>3</v>
-      </c>
+      <c r="B9" s="61"/>
       <c r="C9" s="54"/>
       <c r="D9" s="54"/>
       <c r="E9" s="56"/>
       <c r="F9" s="13">
         <f>SUM(B9:E9)</f>
-        <v>3</v>
-      </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="35"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67"/>
       <c r="K9" s="11">
         <f>SUM(G9:J9)</f>
         <v>0</v>
       </c>
       <c r="L9" s="5">
         <f>SUM(F9+K9)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>2</v>
       </c>
-      <c r="B10" s="40"/>
+      <c r="B10" s="62"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
       <c r="E10" s="39"/>
@@ -6102,10 +8985,10 @@
         <f t="shared" ref="F10:F39" si="0">SUM(B10:E10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
       <c r="K10" s="11">
         <f t="shared" ref="K10:K39" si="1">SUM(G10:J10)</f>
         <v>0</v>
@@ -6119,7 +9002,7 @@
       <c r="A11" s="47">
         <v>3</v>
       </c>
-      <c r="B11" s="40"/>
+      <c r="B11" s="62"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
       <c r="E11" s="39"/>
@@ -6127,10 +9010,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
       <c r="K11" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6144,7 +9027,7 @@
       <c r="A12" s="47">
         <v>4</v>
       </c>
-      <c r="B12" s="40"/>
+      <c r="B12" s="62"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
       <c r="E12" s="39"/>
@@ -6152,10 +9035,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
       <c r="K12" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6169,38 +9052,32 @@
       <c r="A13" s="47">
         <v>5</v>
       </c>
-      <c r="B13" s="40">
-        <v>2</v>
-      </c>
+      <c r="B13" s="62"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
       <c r="E13" s="39"/>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G13" s="38">
-        <v>3</v>
-      </c>
-      <c r="H13" s="38"/>
-      <c r="I13" s="53">
-        <v>1</v>
-      </c>
-      <c r="J13" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="38"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
       <c r="K13" s="11">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>6</v>
       </c>
-      <c r="B14" s="40"/>
+      <c r="B14" s="62"/>
       <c r="C14" s="42"/>
       <c r="D14" s="42"/>
       <c r="E14" s="39"/>
@@ -6209,9 +9086,9 @@
         <v>0</v>
       </c>
       <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="38"/>
       <c r="K14" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6225,36 +9102,32 @@
       <c r="A15" s="47">
         <v>7</v>
       </c>
-      <c r="B15" s="40">
-        <v>5</v>
-      </c>
+      <c r="B15" s="62"/>
       <c r="C15" s="42"/>
       <c r="D15" s="42"/>
       <c r="E15" s="39"/>
       <c r="F15" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G15" s="38">
-        <v>7</v>
-      </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="38"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="38"/>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="47">
         <v>8</v>
       </c>
-      <c r="B16" s="40"/>
+      <c r="B16" s="62"/>
       <c r="C16" s="42"/>
       <c r="D16" s="42"/>
       <c r="E16" s="39"/>
@@ -6262,28 +9135,24 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="38">
-        <v>12</v>
-      </c>
-      <c r="H16" s="38">
-        <v>1</v>
-      </c>
-      <c r="I16" s="53"/>
-      <c r="J16" s="53"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="38"/>
       <c r="K16" s="11">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="47">
         <v>9</v>
       </c>
-      <c r="B17" s="40"/>
+      <c r="B17" s="62"/>
       <c r="C17" s="42"/>
       <c r="D17" s="42"/>
       <c r="E17" s="39"/>
@@ -6292,9 +9161,9 @@
         <v>0</v>
       </c>
       <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="38"/>
       <c r="K17" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6308,7 +9177,7 @@
       <c r="A18" s="47">
         <v>10</v>
       </c>
-      <c r="B18" s="40"/>
+      <c r="B18" s="62"/>
       <c r="C18" s="42"/>
       <c r="D18" s="42"/>
       <c r="E18" s="39"/>
@@ -6316,10 +9185,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="38"/>
       <c r="K18" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6333,7 +9202,7 @@
       <c r="A19" s="47">
         <v>11</v>
       </c>
-      <c r="B19" s="40"/>
+      <c r="B19" s="62"/>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
       <c r="E19" s="39"/>
@@ -6341,10 +9210,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="19"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="38"/>
       <c r="K19" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6358,36 +9227,32 @@
       <c r="A20" s="47">
         <v>12</v>
       </c>
-      <c r="B20" s="40">
-        <v>2</v>
-      </c>
+      <c r="B20" s="62"/>
       <c r="C20" s="42"/>
-      <c r="D20" s="42">
-        <v>2</v>
-      </c>
+      <c r="D20" s="42"/>
       <c r="E20" s="39"/>
       <c r="F20" s="13">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="38"/>
       <c r="K20" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="47">
         <v>13</v>
       </c>
-      <c r="B21" s="40"/>
+      <c r="B21" s="62"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
       <c r="E21" s="39"/>
@@ -6395,122 +9260,110 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="21">
-        <v>2</v>
-      </c>
-      <c r="H21" s="41"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="38"/>
       <c r="K21" s="11">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="47">
         <v>14</v>
       </c>
-      <c r="B22" s="40">
-        <v>1</v>
-      </c>
+      <c r="B22" s="62"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
       <c r="E22" s="39"/>
       <c r="F22" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G22" s="21"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="38"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="38"/>
       <c r="K22" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="47">
         <v>15</v>
       </c>
-      <c r="B23" s="40">
-        <v>2</v>
-      </c>
+      <c r="B23" s="62"/>
       <c r="C23" s="42"/>
       <c r="D23" s="42"/>
       <c r="E23" s="39"/>
       <c r="F23" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G23" s="19">
-        <v>1</v>
-      </c>
-      <c r="H23" s="53">
-        <v>1</v>
-      </c>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="38"/>
       <c r="K23" s="11">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="47">
         <v>16</v>
       </c>
-      <c r="B24" s="40">
-        <v>2</v>
-      </c>
+      <c r="B24" s="62"/>
       <c r="C24" s="42"/>
       <c r="D24" s="42"/>
       <c r="E24" s="39"/>
       <c r="F24" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="38"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="38"/>
       <c r="K24" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="47">
         <v>17</v>
       </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="63"/>
       <c r="D25" s="42"/>
       <c r="E25" s="39"/>
       <c r="F25" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="38"/>
       <c r="K25" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6524,36 +9377,32 @@
       <c r="A26" s="47">
         <v>18</v>
       </c>
-      <c r="B26" s="40">
-        <v>2</v>
-      </c>
+      <c r="B26" s="62"/>
       <c r="C26" s="42"/>
       <c r="D26" s="42"/>
       <c r="E26" s="39"/>
       <c r="F26" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G26" s="19"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53">
-        <v>1</v>
-      </c>
-      <c r="J26" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="38"/>
       <c r="K26" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="47">
         <v>19</v>
       </c>
-      <c r="B27" s="40"/>
+      <c r="B27" s="62"/>
       <c r="C27" s="42"/>
       <c r="D27" s="42"/>
       <c r="E27" s="39"/>
@@ -6561,10 +9410,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G27" s="19"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="38"/>
       <c r="K27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6578,7 +9427,7 @@
       <c r="A28" s="47">
         <v>20</v>
       </c>
-      <c r="B28" s="40"/>
+      <c r="B28" s="62"/>
       <c r="C28" s="42"/>
       <c r="D28" s="42"/>
       <c r="E28" s="39"/>
@@ -6586,10 +9435,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G28" s="19"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="38"/>
       <c r="K28" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6603,90 +9452,82 @@
       <c r="A29" s="47">
         <v>21</v>
       </c>
-      <c r="B29" s="40">
-        <v>1</v>
-      </c>
+      <c r="B29" s="62"/>
       <c r="C29" s="42"/>
       <c r="D29" s="42"/>
       <c r="E29" s="39"/>
       <c r="F29" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G29" s="19">
-        <v>9</v>
-      </c>
-      <c r="H29" s="53"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="38"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="38"/>
       <c r="K29" s="11">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="47">
         <v>22</v>
       </c>
-      <c r="B30" s="40">
-        <v>6</v>
-      </c>
+      <c r="B30" s="62"/>
       <c r="C30" s="42"/>
       <c r="D30" s="42"/>
       <c r="E30" s="39"/>
       <c r="F30" s="13">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="G30" s="19"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="38"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="38"/>
       <c r="K30" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="47">
         <v>23</v>
       </c>
-      <c r="B31" s="40">
-        <v>1</v>
-      </c>
+      <c r="B31" s="62"/>
       <c r="C31" s="42"/>
       <c r="D31" s="42"/>
       <c r="E31" s="39"/>
       <c r="F31" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G31" s="19"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="38"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
       <c r="K31" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="47">
         <v>24</v>
       </c>
-      <c r="B32" s="40"/>
+      <c r="B32" s="62"/>
       <c r="C32" s="42"/>
       <c r="D32" s="42"/>
       <c r="E32" s="39"/>
@@ -6694,10 +9535,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G32" s="19"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
       <c r="K32" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6711,7 +9552,7 @@
       <c r="A33" s="47">
         <v>25</v>
       </c>
-      <c r="B33" s="40"/>
+      <c r="B33" s="62"/>
       <c r="C33" s="42"/>
       <c r="D33" s="42"/>
       <c r="E33" s="39"/>
@@ -6719,174 +9560,160 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G33" s="19">
-        <v>10</v>
-      </c>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
       <c r="K33" s="11">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="47">
         <v>26</v>
       </c>
-      <c r="B34" s="40">
-        <v>4</v>
-      </c>
+      <c r="B34" s="62"/>
       <c r="C34" s="42"/>
       <c r="D34" s="42"/>
       <c r="E34" s="39"/>
       <c r="F34" s="13">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G34" s="19"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="38"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
       <c r="K34" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L34" s="5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="47">
         <v>27</v>
       </c>
-      <c r="B35" s="44">
-        <v>1</v>
-      </c>
+      <c r="B35" s="62"/>
       <c r="C35" s="42"/>
       <c r="D35" s="42"/>
       <c r="E35" s="39"/>
       <c r="F35" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G35" s="30"/>
-      <c r="H35" s="38">
-        <v>1</v>
-      </c>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="68"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
       <c r="K35" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="47">
         <v>28</v>
       </c>
-      <c r="B36" s="44">
-        <v>3</v>
-      </c>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="58"/>
+      <c r="B36" s="62"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="39"/>
       <c r="F36" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G36" s="19"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="38"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
       <c r="K36" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="47">
         <v>29</v>
       </c>
-      <c r="B37" s="44"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="58"/>
+      <c r="B37" s="62"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="39"/>
       <c r="F37" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G37" s="19">
-        <v>3</v>
-      </c>
-      <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
       <c r="K37" s="11">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="47">
         <v>30</v>
       </c>
-      <c r="B38" s="44">
-        <v>2</v>
-      </c>
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="58"/>
+      <c r="B38" s="62"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="39"/>
       <c r="F38" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G38" s="19"/>
-      <c r="H38" s="53"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="38"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
       <c r="K38" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="49">
         <v>31</v>
       </c>
-      <c r="B39" s="45"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="60"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="66"/>
       <c r="F39" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G39" s="19"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
       <c r="K39" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -6900,7 +9727,7 @@
       <c r="A40" s="48"/>
       <c r="B40" s="52">
         <f>SUM(B9:B39)</f>
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="C40" s="52">
         <f t="shared" ref="C40:E40" si="3">SUM(C9:C39)</f>
@@ -6908,7 +9735,7 @@
       </c>
       <c r="D40" s="52">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" s="52">
         <f t="shared" si="3"/>
@@ -6916,19 +9743,19 @@
       </c>
       <c r="F40" s="51">
         <f>SUM(F9:F39)</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G40" s="12">
         <f>SUM(G9:G39)</f>
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" ref="H40:L40" si="4">SUM(H9:H39)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I40" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12">
         <f t="shared" si="4"/>
@@ -6936,11 +9763,11 @@
       </c>
       <c r="K40" s="12">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="4"/>
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6958,149 +9785,149 @@
       <c r="L41" s="9"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="74"/>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="75" t="s">
+      <c r="A42" s="80"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="76"/>
-      <c r="I42" s="76" t="s">
+      <c r="H42" s="82"/>
+      <c r="I42" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="J42" s="77"/>
+      <c r="J42" s="83"/>
       <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
-      <c r="B43" s="61" t="s">
+      <c r="B43" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="62"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="72">
-        <v>169</v>
-      </c>
-      <c r="H43" s="78"/>
-      <c r="I43" s="79"/>
-      <c r="J43" s="80"/>
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="85"/>
+      <c r="G43" s="86">
+        <v>61</v>
+      </c>
+      <c r="H43" s="87"/>
+      <c r="I43" s="88"/>
+      <c r="J43" s="89"/>
       <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
-      <c r="B44" s="61" t="s">
+      <c r="B44" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="62"/>
-      <c r="E44" s="62"/>
-      <c r="F44" s="62"/>
-      <c r="G44" s="65">
-        <v>1</v>
-      </c>
-      <c r="H44" s="64"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="64"/>
+      <c r="C44" s="85"/>
+      <c r="D44" s="85"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="85"/>
+      <c r="G44" s="90">
+        <v>0</v>
+      </c>
+      <c r="H44" s="91"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="91"/>
       <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
-      <c r="B45" s="69" t="s">
+      <c r="B45" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="70">
-        <v>0</v>
-      </c>
-      <c r="H45" s="71"/>
-      <c r="I45" s="72"/>
-      <c r="J45" s="73"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="93">
+        <v>0</v>
+      </c>
+      <c r="H45" s="94"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="95"/>
       <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="61" t="s">
+      <c r="B46" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="63">
+      <c r="C46" s="85"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="96">
         <f>L40+G45</f>
-        <v>91</v>
-      </c>
-      <c r="H46" s="64"/>
-      <c r="I46" s="65"/>
-      <c r="J46" s="64"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="91"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="91"/>
       <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
-      <c r="B47" s="61" t="s">
+      <c r="B47" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="62"/>
-      <c r="D47" s="62"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="62"/>
-      <c r="G47" s="63">
+      <c r="C47" s="85"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="96">
         <f>G43+G44-G46</f>
-        <v>79</v>
-      </c>
-      <c r="H47" s="64"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="64"/>
+        <v>61</v>
+      </c>
+      <c r="H47" s="91"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="91"/>
       <c r="K47" s="7"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="61" t="s">
+      <c r="B48" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="62"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="63">
-        <v>78</v>
-      </c>
-      <c r="H48" s="64"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="64"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="85"/>
+      <c r="E48" s="85"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="96">
+        <v>61</v>
+      </c>
+      <c r="H48" s="91"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="91"/>
       <c r="K48" s="7"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
-      <c r="B49" s="61" t="s">
+      <c r="B49" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="62"/>
-      <c r="D49" s="62"/>
-      <c r="E49" s="62"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="66">
+      <c r="C49" s="85"/>
+      <c r="D49" s="85"/>
+      <c r="E49" s="85"/>
+      <c r="F49" s="85"/>
+      <c r="G49" s="97">
         <f>G47-G48</f>
-        <v>1</v>
-      </c>
-      <c r="H49" s="67"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="67"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="98"/>
+      <c r="I49" s="99"/>
+      <c r="J49" s="98"/>
       <c r="K49" s="7"/>
       <c r="L49" s="2"/>
     </row>
@@ -7124,49 +9951,44 @@
     </row>
     <row r="51" spans="1:12" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>33</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L8"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="G2:L2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="G3:L3"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
